--- a/included/leaguehistory.xlsx
+++ b/included/leaguehistory.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aflyn\repos\Baseball\FantasySgpSystem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FantBaseball\FantasySgpSystem\included\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDC89CF9-AE26-4CE5-8359-9970099BD13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F706174-6BD4-40FA-848F-270190C92A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4710" windowWidth="29040" windowHeight="15720" xr2:uid="{CDE96B8F-12BE-474E-931C-48604B977C2E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{CDE96B8F-12BE-474E-931C-48604B977C2E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Historical Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Parameters" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="43">
   <si>
     <t>AVERAGE</t>
   </si>
@@ -467,9 +468,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -482,6 +480,9 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -490,35 +491,7 @@
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -1127,12 +1100,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA00790-540E-4A47-8DFE-0C5A82FABDCD}">
   <dimension ref="A1:AB77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="16" max="16" width="9.140625" style="1"/>
+    <col min="16" max="16" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>2023</v>
       </c>
@@ -1151,7 +1124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>2</v>
       </c>
@@ -1225,7 +1198,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1317,7 +1290,7 @@
         <v>146.71428571428572</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1409,7 +1382,7 @@
         <v>121.28571428571429</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1501,7 +1474,7 @@
         <v>113.42857142857143</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1593,7 +1566,7 @@
         <v>108.71428571428571</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1685,7 +1658,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1777,7 +1750,7 @@
         <v>97.857142857142861</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1869,7 +1842,7 @@
         <v>95.142857142857139</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1961,7 +1934,7 @@
         <v>84.285714285714292</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2053,7 +2026,7 @@
         <v>75.714285714285708</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2145,7 +2118,7 @@
         <v>69.142857142857139</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2237,7 +2210,7 @@
         <v>56.142857142857146</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2329,7 +2302,7 @@
         <v>41.142857142857146</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B15">
         <f t="shared" ref="B15:M15" si="4">-1*SLOPE(B4:B13,$A$4:$A$13)</f>
         <v>11.406060606060606</v>
@@ -2379,7 +2352,7 @@
         <v>6.1515151515151514</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B16">
         <f t="shared" ref="B16:G16" si="5">B15/$D$15</f>
         <v>0.79242105263157891</v>
@@ -2429,7 +2402,7 @@
         <v>0.12437201323367233</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2022</v>
       </c>
@@ -2485,7 +2458,7 @@
         <v>92.714285714285708</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -2574,7 +2547,7 @@
         <v>10.301587301587301</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -2666,7 +2639,7 @@
         <v>28.089567627925675</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2758,7 +2731,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2850,7 +2823,7 @@
         <v>789.02380952380997</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>4</v>
       </c>
@@ -2892,7 +2865,7 @@
       </c>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>5</v>
       </c>
@@ -2942,7 +2915,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>6</v>
       </c>
@@ -3007,7 +2980,7 @@
         <v>18.377777777777769</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>7</v>
       </c>
@@ -3054,7 +3027,7 @@
         <v>9.2242424242424246</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>8</v>
       </c>
@@ -3146,7 +3119,7 @@
         <v>18.377777777777769</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>9</v>
       </c>
@@ -3238,7 +3211,7 @@
         <v>6.7887445887445885</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>10</v>
       </c>
@@ -3330,7 +3303,7 @@
         <v>0.11691119460845709</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>11</v>
       </c>
@@ -3371,7 +3344,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>12</v>
       </c>
@@ -3463,7 +3436,7 @@
         <v>8.0142857142857142</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B31">
         <f t="shared" ref="B31:M31" si="13">-1*SLOPE(B20:B29,$A$20:$A$29)</f>
         <v>10.32121212121212</v>
@@ -3564,7 +3537,7 @@
         <v>9.5974025974025992</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B32">
         <f t="shared" ref="B32:G32" si="15">B31/$D$31</f>
         <v>0.53858317520556609</v>
@@ -3665,7 +3638,7 @@
         <v>146.71428571428572</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2021</v>
       </c>
@@ -3721,7 +3694,7 @@
         <v>41.142857142857146</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="14" t="s">
         <v>29</v>
       </c>
@@ -3813,7 +3786,7 @@
         <v>30.29691423659164</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="14">
         <v>1</v>
       </c>
@@ -3893,7 +3866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="14">
         <v>2</v>
       </c>
@@ -3970,7 +3943,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14">
         <v>3</v>
       </c>
@@ -4062,7 +4035,7 @@
         <v>113.42857142857143</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="14">
         <v>4</v>
       </c>
@@ -4154,7 +4127,7 @@
         <v>12.603174603174603</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="61.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="14">
         <v>5</v>
       </c>
@@ -4246,7 +4219,7 @@
         <v>116.23203463203461</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:28" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="14">
         <v>6</v>
       </c>
@@ -4338,7 +4311,7 @@
         <v>12.914670514670512</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="14">
         <v>7</v>
       </c>
@@ -4430,7 +4403,7 @@
         <v>74.071428571428569</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="14">
         <v>8</v>
       </c>
@@ -4522,7 +4495,7 @@
         <v>109.89285714285714</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="14">
         <v>9</v>
       </c>
@@ -4614,7 +4587,7 @@
         <v>35.821428571428569</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="14">
         <v>10</v>
       </c>
@@ -4706,7 +4679,7 @@
         <v>38.25</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="14">
         <v>11</v>
       </c>
@@ -4798,7 +4771,7 @@
         <v>145.71428571428572</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="14">
         <v>12</v>
       </c>
@@ -4839,7 +4812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B47">
         <f t="shared" ref="B47:G47" si="27">-1*SLOPE(B36:B45,$A$36:$A$45)</f>
         <v>18.145454545454545</v>
@@ -4889,7 +4862,7 @@
         <v>10.036363636363637</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B48">
         <f t="shared" ref="B48:G48" si="29">B47/$D$47</f>
         <v>1.139269406392694</v>
@@ -4939,564 +4912,564 @@
         <v>0.18769126147568854</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="51" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2024</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20" t="s">
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="20"/>
-    </row>
-    <row r="52" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="21" t="s">
+      <c r="I51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="24"/>
+    </row>
+    <row r="52" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="C52" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D52" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E52" s="21" t="s">
+      <c r="E52" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="21" t="s">
+      <c r="F52" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="G52" s="21" t="s">
+      <c r="G52" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="21" t="s">
+      <c r="H52" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I52" s="21" t="s">
+      <c r="I52" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="J52" s="21" t="s">
+      <c r="J52" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K52" s="21" t="s">
+      <c r="K52" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="L52" s="21" t="s">
+      <c r="L52" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="M52" s="21" t="s">
+      <c r="M52" s="20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="22">
+    <row r="53" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="21">
         <v>981</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="21">
         <v>321</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="21">
         <v>997</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E53" s="21">
         <v>152</v>
       </c>
-      <c r="F53" s="22">
+      <c r="F53" s="21">
         <v>0.33069999999999999</v>
       </c>
-      <c r="G53" s="22">
+      <c r="G53" s="21">
         <v>0.4577</v>
       </c>
-      <c r="H53" s="22">
+      <c r="H53" s="21">
         <v>1778</v>
       </c>
-      <c r="I53" s="22">
+      <c r="I53" s="21">
         <v>133</v>
       </c>
-      <c r="J53" s="22">
+      <c r="J53" s="21">
         <v>3.4460000000000002</v>
       </c>
-      <c r="K53" s="22">
+      <c r="K53" s="21">
         <v>1.159</v>
       </c>
-      <c r="L53" s="22">
+      <c r="L53" s="21">
         <v>3.4129999999999998</v>
       </c>
-      <c r="M53" s="22">
+      <c r="M53" s="21">
         <v>123</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="23">
+    <row r="54" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="22">
         <v>1084</v>
       </c>
-      <c r="C54" s="23">
+      <c r="C54" s="22">
         <v>355</v>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="22">
         <v>1091</v>
       </c>
-      <c r="E54" s="23">
+      <c r="E54" s="22">
         <v>85</v>
       </c>
-      <c r="F54" s="23">
+      <c r="F54" s="22">
         <v>0.33950000000000002</v>
       </c>
-      <c r="G54" s="23">
+      <c r="G54" s="22">
         <v>0.4476</v>
       </c>
-      <c r="H54" s="23">
+      <c r="H54" s="22">
         <v>1666</v>
       </c>
-      <c r="I54" s="23">
+      <c r="I54" s="22">
         <v>108</v>
       </c>
-      <c r="J54" s="23">
+      <c r="J54" s="22">
         <v>3.621</v>
       </c>
-      <c r="K54" s="23">
+      <c r="K54" s="22">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L54" s="23">
+      <c r="L54" s="22">
         <v>4.1440000000000001</v>
       </c>
-      <c r="M54" s="23">
+      <c r="M54" s="22">
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="22">
+    <row r="55" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="21">
         <v>969</v>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="21">
         <v>279</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="21">
         <v>941</v>
       </c>
-      <c r="E55" s="22">
+      <c r="E55" s="21">
         <v>111</v>
       </c>
-      <c r="F55" s="22">
+      <c r="F55" s="21">
         <v>0.31969999999999998</v>
       </c>
-      <c r="G55" s="22">
+      <c r="G55" s="21">
         <v>0.4214</v>
       </c>
-      <c r="H55" s="22">
+      <c r="H55" s="21">
         <v>1942</v>
       </c>
-      <c r="I55" s="22">
+      <c r="I55" s="21">
         <v>155</v>
       </c>
-      <c r="J55" s="22">
+      <c r="J55" s="21">
         <v>3.3530000000000002</v>
       </c>
-      <c r="K55" s="22">
+      <c r="K55" s="21">
         <v>1.1399999999999999</v>
       </c>
-      <c r="L55" s="22">
+      <c r="L55" s="21">
         <v>3.6230000000000002</v>
       </c>
-      <c r="M55" s="22">
+      <c r="M55" s="21">
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="22">
+    <row r="56" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="21">
         <v>1015</v>
       </c>
-      <c r="C56" s="22">
+      <c r="C56" s="21">
         <v>238</v>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="21">
         <v>905</v>
       </c>
-      <c r="E56" s="22">
+      <c r="E56" s="21">
         <v>242</v>
       </c>
-      <c r="F56" s="22">
+      <c r="F56" s="21">
         <v>0.314</v>
       </c>
-      <c r="G56" s="22">
+      <c r="G56" s="21">
         <v>0.40739999999999998</v>
       </c>
-      <c r="H56" s="22">
+      <c r="H56" s="21">
         <v>1357</v>
       </c>
-      <c r="I56" s="22">
+      <c r="I56" s="21">
         <v>98</v>
       </c>
-      <c r="J56" s="22">
+      <c r="J56" s="21">
         <v>4.0110000000000001</v>
       </c>
-      <c r="K56" s="22">
+      <c r="K56" s="21">
         <v>1.204</v>
       </c>
-      <c r="L56" s="22">
+      <c r="L56" s="21">
         <v>3.0289999999999999</v>
       </c>
-      <c r="M56" s="22">
+      <c r="M56" s="21">
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="22">
+    <row r="57" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="21">
         <v>1049</v>
       </c>
-      <c r="C57" s="22">
+      <c r="C57" s="21">
         <v>295</v>
       </c>
-      <c r="D57" s="22">
+      <c r="D57" s="21">
         <v>1007</v>
       </c>
-      <c r="E57" s="22">
+      <c r="E57" s="21">
         <v>177</v>
       </c>
-      <c r="F57" s="22">
+      <c r="F57" s="21">
         <v>0.32640000000000002</v>
       </c>
-      <c r="G57" s="22">
+      <c r="G57" s="21">
         <v>0.43430000000000002</v>
       </c>
-      <c r="H57" s="22">
+      <c r="H57" s="21">
         <v>1419</v>
       </c>
-      <c r="I57" s="22">
+      <c r="I57" s="21">
         <v>83</v>
       </c>
-      <c r="J57" s="22">
+      <c r="J57" s="21">
         <v>4.1109999999999998</v>
       </c>
-      <c r="K57" s="22">
+      <c r="K57" s="21">
         <v>1.2709999999999999</v>
       </c>
-      <c r="L57" s="22">
+      <c r="L57" s="21">
         <v>3.21</v>
       </c>
-      <c r="M57" s="22">
+      <c r="M57" s="21">
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="22">
+    <row r="58" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="21">
         <v>1065</v>
       </c>
-      <c r="C58" s="22">
+      <c r="C58" s="21">
         <v>249</v>
       </c>
-      <c r="D58" s="22">
+      <c r="D58" s="21">
         <v>975</v>
       </c>
-      <c r="E58" s="22">
+      <c r="E58" s="21">
         <v>250</v>
       </c>
-      <c r="F58" s="22">
+      <c r="F58" s="21">
         <v>0.32369999999999999</v>
       </c>
-      <c r="G58" s="22">
+      <c r="G58" s="21">
         <v>0.4234</v>
       </c>
-      <c r="H58" s="22">
+      <c r="H58" s="21">
         <v>1278</v>
       </c>
-      <c r="I58" s="22">
+      <c r="I58" s="21">
         <v>79</v>
       </c>
-      <c r="J58" s="22">
+      <c r="J58" s="21">
         <v>3.9569999999999999</v>
       </c>
-      <c r="K58" s="22">
+      <c r="K58" s="21">
         <v>1.2689999999999999</v>
       </c>
-      <c r="L58" s="22">
+      <c r="L58" s="21">
         <v>2.766</v>
       </c>
-      <c r="M58" s="22">
+      <c r="M58" s="21">
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="22">
+    <row r="59" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="21">
         <v>930</v>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="21">
         <v>244</v>
       </c>
-      <c r="D59" s="22">
+      <c r="D59" s="21">
         <v>939</v>
       </c>
-      <c r="E59" s="22">
+      <c r="E59" s="21">
         <v>132</v>
       </c>
-      <c r="F59" s="22">
+      <c r="F59" s="21">
         <v>0.31569999999999998</v>
       </c>
-      <c r="G59" s="22">
+      <c r="G59" s="21">
         <v>0.41880000000000001</v>
       </c>
-      <c r="H59" s="22">
+      <c r="H59" s="21">
         <v>1422</v>
       </c>
-      <c r="I59" s="22">
+      <c r="I59" s="21">
         <v>103</v>
       </c>
-      <c r="J59" s="22">
+      <c r="J59" s="21">
         <v>3.6739999999999999</v>
       </c>
-      <c r="K59" s="22">
+      <c r="K59" s="21">
         <v>1.1739999999999999</v>
       </c>
-      <c r="L59" s="22">
+      <c r="L59" s="21">
         <v>3.2170000000000001</v>
       </c>
-      <c r="M59" s="22">
+      <c r="M59" s="21">
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="22">
+    <row r="60" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="21">
         <v>1070</v>
       </c>
-      <c r="C60" s="22">
+      <c r="C60" s="21">
         <v>295</v>
       </c>
-      <c r="D60" s="22">
+      <c r="D60" s="21">
         <v>985</v>
       </c>
-      <c r="E60" s="22">
+      <c r="E60" s="21">
         <v>193</v>
       </c>
-      <c r="F60" s="22">
+      <c r="F60" s="21">
         <v>0.33350000000000002</v>
       </c>
-      <c r="G60" s="22">
+      <c r="G60" s="21">
         <v>0.43619999999999998</v>
       </c>
-      <c r="H60" s="22">
+      <c r="H60" s="21">
         <v>1598</v>
       </c>
-      <c r="I60" s="22">
+      <c r="I60" s="21">
         <v>113</v>
       </c>
-      <c r="J60" s="22">
+      <c r="J60" s="21">
         <v>4.28</v>
       </c>
-      <c r="K60" s="22">
+      <c r="K60" s="21">
         <v>1.272</v>
       </c>
-      <c r="L60" s="22">
+      <c r="L60" s="21">
         <v>2.9809999999999999</v>
       </c>
-      <c r="M60" s="22">
+      <c r="M60" s="21">
         <v>77</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="22">
+    <row r="61" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="21">
         <v>976</v>
       </c>
-      <c r="C61" s="22">
+      <c r="C61" s="21">
         <v>285</v>
       </c>
-      <c r="D61" s="22">
+      <c r="D61" s="21">
         <v>951</v>
       </c>
-      <c r="E61" s="22">
+      <c r="E61" s="21">
         <v>134</v>
       </c>
-      <c r="F61" s="22">
+      <c r="F61" s="21">
         <v>0.32329999999999998</v>
       </c>
-      <c r="G61" s="22">
+      <c r="G61" s="21">
         <v>0.44069999999999998</v>
       </c>
-      <c r="H61" s="22">
+      <c r="H61" s="21">
         <v>874</v>
       </c>
-      <c r="I61" s="22">
+      <c r="I61" s="21">
         <v>56</v>
       </c>
-      <c r="J61" s="22">
+      <c r="J61" s="21">
         <v>4.1289999999999996</v>
       </c>
-      <c r="K61" s="22">
+      <c r="K61" s="21">
         <v>1.272</v>
       </c>
-      <c r="L61" s="22">
+      <c r="L61" s="21">
         <v>2.5329999999999999</v>
       </c>
-      <c r="M61" s="22">
+      <c r="M61" s="21">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="22">
+    <row r="62" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="21">
         <v>908</v>
       </c>
-      <c r="C62" s="22">
+      <c r="C62" s="21">
         <v>203</v>
       </c>
-      <c r="D62" s="22">
+      <c r="D62" s="21">
         <v>889</v>
       </c>
-      <c r="E62" s="22">
+      <c r="E62" s="21">
         <v>158</v>
       </c>
-      <c r="F62" s="22">
+      <c r="F62" s="21">
         <v>0.32969999999999999</v>
       </c>
-      <c r="G62" s="22">
+      <c r="G62" s="21">
         <v>0.4017</v>
       </c>
-      <c r="H62" s="22">
+      <c r="H62" s="21">
         <v>1192</v>
       </c>
-      <c r="I62" s="22">
+      <c r="I62" s="21">
         <v>77</v>
       </c>
-      <c r="J62" s="22">
+      <c r="J62" s="21">
         <v>3.802</v>
       </c>
-      <c r="K62" s="22">
+      <c r="K62" s="21">
         <v>1.133</v>
       </c>
-      <c r="L62" s="22">
+      <c r="L62" s="21">
         <v>3.883</v>
       </c>
-      <c r="M62" s="22">
+      <c r="M62" s="21">
         <v>120</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="22">
+    <row r="63" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="21">
         <v>919</v>
       </c>
-      <c r="C63" s="22">
+      <c r="C63" s="21">
         <v>270</v>
       </c>
-      <c r="D63" s="22">
+      <c r="D63" s="21">
         <v>871</v>
       </c>
-      <c r="E63" s="22">
+      <c r="E63" s="21">
         <v>242</v>
       </c>
-      <c r="F63" s="22">
+      <c r="F63" s="21">
         <v>0.31540000000000001</v>
       </c>
-      <c r="G63" s="22">
+      <c r="G63" s="21">
         <v>0.41739999999999999</v>
       </c>
-      <c r="H63" s="22">
+      <c r="H63" s="21">
         <v>1453</v>
       </c>
-      <c r="I63" s="22">
+      <c r="I63" s="21">
         <v>101</v>
       </c>
-      <c r="J63" s="22">
+      <c r="J63" s="21">
         <v>3.7610000000000001</v>
       </c>
-      <c r="K63" s="22">
+      <c r="K63" s="21">
         <v>1.1779999999999999</v>
       </c>
-      <c r="L63" s="22">
+      <c r="L63" s="21">
         <v>3.34</v>
       </c>
-      <c r="M63" s="22">
+      <c r="M63" s="21">
         <v>93</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="24">
+    <row r="64" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="23">
         <v>907</v>
       </c>
-      <c r="C64" s="24">
+      <c r="C64" s="23">
         <v>251</v>
       </c>
-      <c r="D64" s="24">
+      <c r="D64" s="23">
         <v>846</v>
       </c>
-      <c r="E64" s="24">
+      <c r="E64" s="23">
         <v>125</v>
       </c>
-      <c r="F64" s="24">
+      <c r="F64" s="23">
         <v>0.31359999999999999</v>
       </c>
-      <c r="G64" s="24">
+      <c r="G64" s="23">
         <v>0.41410000000000002</v>
       </c>
-      <c r="H64" s="24">
+      <c r="H64" s="23">
         <v>1231</v>
       </c>
-      <c r="I64" s="24">
+      <c r="I64" s="23">
         <v>70</v>
       </c>
-      <c r="J64" s="24">
+      <c r="J64" s="23">
         <v>3.379</v>
       </c>
-      <c r="K64" s="24">
+      <c r="K64" s="23">
         <v>1.1040000000000001</v>
       </c>
-      <c r="L64" s="24">
+      <c r="L64" s="23">
         <v>3.6419999999999999</v>
       </c>
-      <c r="M64" s="24">
+      <c r="M64" s="23">
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2024</v>
       </c>
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D65" s="21" t="s">
+      <c r="D65" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="21" t="s">
+      <c r="E65" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="21" t="s">
+      <c r="F65" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="21" t="s">
+      <c r="G65" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="21" t="s">
+      <c r="H65" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="I65" s="21" t="s">
+      <c r="I65" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="J65" s="21" t="s">
+      <c r="J65" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K65" s="21" t="s">
+      <c r="K65" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="L65" s="21" t="s">
+      <c r="L65" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="M65" s="21" t="s">
+      <c r="M65" s="20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B66" cm="1">
         <f t="array" ref="B66:B77">_xlfn._xlws.SORT(B53:B64,,-1)</f>
         <v>1084</v>
@@ -5546,7 +5519,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>1070</v>
       </c>
@@ -5584,7 +5557,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>1065</v>
       </c>
@@ -5622,7 +5595,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>1049</v>
       </c>
@@ -5660,7 +5633,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>1015</v>
       </c>
@@ -5698,7 +5671,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>981</v>
       </c>
@@ -5736,7 +5709,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>976</v>
       </c>
@@ -5774,7 +5747,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>969</v>
       </c>
@@ -5812,7 +5785,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>930</v>
       </c>
@@ -5850,7 +5823,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>919</v>
       </c>
@@ -5888,7 +5861,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>908</v>
       </c>
@@ -5926,7 +5899,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>907</v>
       </c>
@@ -5969,31 +5942,181 @@
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="H51:M51"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q3:X14">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
-      <formula>Q$45</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="lessThan">
+  <conditionalFormatting sqref="Q3:AB14">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>Q$44</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA3:AB14">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
-      <formula>AA$44</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
-      <formula>AA$45</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y3:Z14">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>Y$44</formula>
-    </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>Y$45</formula>
+      <formula>Q$45</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9734E317-61B8-40AC-9651-51DC5AB8F31B}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1">
+        <f>'Historical Data'!$Q26</f>
+        <v>70.609523809523807</v>
+      </c>
+      <c r="C1">
+        <f>'Historical Data'!$Q27</f>
+        <v>15.683982683982686</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <f>'Historical Data'!$R26</f>
+        <v>18.566300366300368</v>
+      </c>
+      <c r="C2">
+        <f>'Historical Data'!$R27</f>
+        <v>7.2874458874458883</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <f>'Historical Data'!$S26</f>
+        <v>67.730402930402946</v>
+      </c>
+      <c r="C3">
+        <f>'Historical Data'!$S27</f>
+        <v>15.613852813852809</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <f>'Historical Data'!$T26</f>
+        <v>7.509743589743592</v>
+      </c>
+      <c r="C4">
+        <f>'Historical Data'!$T27</f>
+        <v>12.555151515151515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <f>'Historical Data'!$U26</f>
+        <v>0.3165885714285715</v>
+      </c>
+      <c r="C5">
+        <f>'Historical Data'!$U27</f>
+        <v>2.0805194805194839E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <f>'Historical Data'!$V26</f>
+        <v>0.41529809523809524</v>
+      </c>
+      <c r="C6">
+        <f>'Historical Data'!$V27</f>
+        <v>3.3972294372294379E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <f>'Historical Data'!$W26</f>
+        <v>94.228571428571442</v>
+      </c>
+      <c r="C7">
+        <f>'Historical Data'!$W27</f>
+        <v>58.067532467532466</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <f>'Historical Data'!$X26</f>
+        <v>7.663492063492062</v>
+      </c>
+      <c r="C8">
+        <f>'Historical Data'!$X27</f>
+        <v>5.3454545454545466</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <f>'Historical Data'!$Y26</f>
+        <v>4.3037047619047613</v>
+      </c>
+      <c r="C9">
+        <f>'Historical Data'!$Y27</f>
+        <v>-8.6045021645021633E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <f>'Historical Data'!$Z26</f>
+        <v>1.2834761904761904</v>
+      </c>
+      <c r="C10">
+        <f>'Historical Data'!$Z27</f>
+        <v>-1.4143722943722932E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <f>'Historical Data'!$AA26</f>
+        <v>2.7619619047619035</v>
+      </c>
+      <c r="C11">
+        <f>'Historical Data'!$AA27</f>
+        <v>9.4032900432900468E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <f>'Historical Data'!$AB26</f>
+        <v>18.377777777777769</v>
+      </c>
+      <c r="C12">
+        <f>'Historical Data'!$AB27</f>
+        <v>6.7887445887445885</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/included/leaguehistory.xlsx
+++ b/included/leaguehistory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FantBaseball\FantasySgpSystem\included\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aflyn\repos\Baseball\FantasySgpSystem\included\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F706174-6BD4-40FA-848F-270190C92A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C6EC73-EF51-4371-A353-82E32C902D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{CDE96B8F-12BE-474E-931C-48604B977C2E}"/>
+    <workbookView xWindow="-57720" yWindow="-4695" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CDE96B8F-12BE-474E-931C-48604B977C2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="45">
   <si>
     <t>AVERAGE</t>
   </si>
@@ -189,12 +189,18 @@
   <si>
     <t>Pitching</t>
   </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>SV_HLD</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,6 +261,33 @@
     <font>
       <b/>
       <sz val="7"/>
+      <color rgb="FF797B7D"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF48494A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF151617"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF797B7D"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FF797B7D"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -423,7 +456,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -481,6 +514,21 @@
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1099,13 +1147,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA00790-540E-4A47-8DFE-0C5A82FABDCD}">
-  <dimension ref="A1:AB77"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AB106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="16" max="16" width="9.109375" style="1"/>
+    <col min="16" max="16" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>2023</v>
       </c>
@@ -1124,7 +1172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
@@ -1198,7 +1246,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1242,55 +1290,55 @@
         <v>1</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:S14" si="0">(3*B66+2*B3+B19+B35)/7</f>
-        <v>1089.7142857142858</v>
+        <f>(4*B95+3*B66+2*B3+B19+B35)/11</f>
+        <v>1074.909090909091</v>
       </c>
       <c r="R3">
-        <f t="shared" si="0"/>
-        <v>334.57142857142856</v>
+        <f>(4*C95+3*C66+2*C3+C19+C35)/11</f>
+        <v>335.09090909090907</v>
       </c>
       <c r="S3">
-        <f t="shared" si="0"/>
-        <v>1084.1428571428571</v>
+        <f t="shared" ref="S3:AB14" si="0">(4*D95+3*D66+2*D3+D19+D35)/11</f>
+        <v>1081.5454545454545</v>
       </c>
       <c r="T3">
-        <f>(3*E66+2*E3)/5</f>
-        <v>235.2</v>
+        <f t="shared" si="0"/>
+        <v>216.18181818181819</v>
       </c>
       <c r="U3">
-        <f>(3*F66+2*F3+F19+F35)/7</f>
-        <v>0.34145714285714285</v>
+        <f t="shared" si="0"/>
+        <v>0.34179999999999999</v>
       </c>
       <c r="V3">
-        <f t="shared" ref="V3:AB14" si="1">(3*G66+2*G3+G19+G35)/7</f>
-        <v>0.4607</v>
+        <f t="shared" si="0"/>
+        <v>0.46048181818181805</v>
       </c>
       <c r="W3">
-        <f t="shared" si="1"/>
-        <v>1848.1428571428571</v>
+        <f t="shared" si="0"/>
+        <v>1800.4545454545455</v>
       </c>
       <c r="X3">
-        <f t="shared" si="1"/>
-        <v>139.42857142857142</v>
+        <f t="shared" si="0"/>
+        <v>132.36363636363637</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="1"/>
-        <v>3.3664285714285715</v>
+        <f t="shared" si="0"/>
+        <v>3.3539090909090912</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="1"/>
-        <v>1.1134285714285714</v>
+        <f t="shared" si="0"/>
+        <v>1.1234545454545455</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="1"/>
-        <v>3.9281428571428569</v>
+        <f t="shared" si="0"/>
+        <v>3.8891818181818181</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="1"/>
-        <v>146.71428571428572</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>138.45454545454547</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1334,55 +1382,55 @@
         <v>2</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="0"/>
-        <v>1078</v>
+        <f t="shared" ref="Q4:Q14" si="1">(4*B96+3*B67+2*B4+B20+B36)/11</f>
+        <v>1066</v>
       </c>
       <c r="R4">
-        <f t="shared" si="0"/>
-        <v>317.71428571428572</v>
+        <f t="shared" ref="R4:R14" si="2">(4*C96+3*C67+2*C4+C20+C36)/11</f>
+        <v>321.81818181818181</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>1028.2857142857142</v>
+        <v>1028.5454545454545</v>
       </c>
       <c r="T4">
-        <f t="shared" ref="T4:T14" si="2">(3*E67+2*E4)/5</f>
-        <v>225.2</v>
+        <f t="shared" si="0"/>
+        <v>205.45454545454547</v>
       </c>
       <c r="U4">
-        <f t="shared" ref="U4:U14" si="3">(3*F67+2*F4+F20+F36)/7</f>
-        <v>0.33787142857142866</v>
+        <f t="shared" si="0"/>
+        <v>0.33784545454545456</v>
       </c>
       <c r="V4">
-        <f t="shared" si="1"/>
-        <v>0.45291428571428577</v>
+        <f t="shared" si="0"/>
+        <v>0.45003636363636362</v>
       </c>
       <c r="W4">
-        <f t="shared" si="1"/>
-        <v>1757.1428571428571</v>
+        <f t="shared" si="0"/>
+        <v>1728.7272727272727</v>
       </c>
       <c r="X4">
-        <f t="shared" si="1"/>
-        <v>124.85714285714286</v>
+        <f t="shared" si="0"/>
+        <v>119.81818181818181</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="1"/>
-        <v>3.4558571428571434</v>
+        <f t="shared" si="0"/>
+        <v>3.525727272727273</v>
       </c>
       <c r="Z4">
-        <f t="shared" si="1"/>
-        <v>1.1478571428571429</v>
+        <f t="shared" si="0"/>
+        <v>1.1577272727272727</v>
       </c>
       <c r="AA4">
-        <f t="shared" si="1"/>
-        <v>3.7545714285714284</v>
+        <f t="shared" si="0"/>
+        <v>3.6532727272727272</v>
       </c>
       <c r="AB4">
-        <f t="shared" si="1"/>
-        <v>121.28571428571429</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>122.27272727272727</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1426,55 +1474,55 @@
         <v>3</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
-        <v>1059.8571428571429</v>
+        <f t="shared" si="1"/>
+        <v>1049.3636363636363</v>
       </c>
       <c r="R5">
-        <f t="shared" si="0"/>
-        <v>303.42857142857144</v>
+        <f t="shared" si="2"/>
+        <v>300</v>
       </c>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>1018.2857142857143</v>
+        <v>1013.0909090909091</v>
       </c>
       <c r="T5">
-        <f t="shared" si="2"/>
-        <v>222</v>
+        <f t="shared" si="0"/>
+        <v>194.81818181818181</v>
       </c>
       <c r="U5">
-        <f t="shared" si="3"/>
-        <v>0.33421428571428569</v>
+        <f t="shared" si="0"/>
+        <v>0.33337272727272732</v>
       </c>
       <c r="V5">
-        <f t="shared" si="1"/>
-        <v>0.4450142857142857</v>
+        <f t="shared" si="0"/>
+        <v>0.44380909090909082</v>
       </c>
       <c r="W5">
-        <f t="shared" si="1"/>
-        <v>1657.7142857142858</v>
+        <f t="shared" si="0"/>
+        <v>1646.5454545454545</v>
       </c>
       <c r="X5">
-        <f t="shared" si="1"/>
-        <v>114.14285714285714</v>
+        <f t="shared" si="0"/>
+        <v>111.18181818181819</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="1"/>
-        <v>3.5199999999999996</v>
+        <f t="shared" si="0"/>
+        <v>3.5865454545454543</v>
       </c>
       <c r="Z5">
-        <f t="shared" si="1"/>
-        <v>1.1564285714285716</v>
+        <f t="shared" si="0"/>
+        <v>1.163909090909091</v>
       </c>
       <c r="AA5">
-        <f t="shared" si="1"/>
-        <v>3.5962857142857141</v>
+        <f t="shared" si="0"/>
+        <v>3.4907272727272725</v>
       </c>
       <c r="AB5">
-        <f t="shared" si="1"/>
-        <v>113.42857142857143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>116.18181818181819</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1518,55 +1566,55 @@
         <v>4</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>1045.4285714285713</v>
+        <f t="shared" si="1"/>
+        <v>1037.6363636363637</v>
       </c>
       <c r="R6">
-        <f t="shared" si="0"/>
-        <v>299</v>
+        <f t="shared" si="2"/>
+        <v>295.72727272727275</v>
       </c>
       <c r="S6">
         <f t="shared" si="0"/>
-        <v>1007.4285714285714</v>
+        <v>998.18181818181813</v>
       </c>
       <c r="T6">
-        <f t="shared" si="2"/>
-        <v>192.6</v>
+        <f t="shared" si="0"/>
+        <v>179.72727272727272</v>
       </c>
       <c r="U6">
-        <f t="shared" si="3"/>
-        <v>0.3334428571428571</v>
+        <f t="shared" si="0"/>
+        <v>0.33160909090909091</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
-        <v>0.4409142857142857</v>
+        <f t="shared" si="0"/>
+        <v>0.44090909090909086</v>
       </c>
       <c r="W6">
-        <f t="shared" si="1"/>
-        <v>1580.7142857142858</v>
+        <f t="shared" si="0"/>
+        <v>1585.909090909091</v>
       </c>
       <c r="X6">
-        <f t="shared" si="1"/>
-        <v>110</v>
+        <f t="shared" si="0"/>
+        <v>108.18181818181819</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="1"/>
-        <v>3.6332857142857145</v>
+        <f t="shared" si="0"/>
+        <v>3.665909090909091</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="1"/>
-        <v>1.1727142857142856</v>
+        <f t="shared" si="0"/>
+        <v>1.1844545454545454</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="1"/>
-        <v>3.5187142857142857</v>
+        <f t="shared" si="0"/>
+        <v>3.4326363636363637</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="1"/>
-        <v>108.71428571428571</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>110.63636363636364</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1610,55 +1658,55 @@
         <v>5</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>1026</v>
+        <f t="shared" si="1"/>
+        <v>1022.3636363636364</v>
       </c>
       <c r="R7">
-        <f t="shared" si="0"/>
-        <v>292.14285714285717</v>
+        <f t="shared" si="2"/>
+        <v>291.36363636363637</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>993.14285714285711</v>
+        <v>988</v>
       </c>
       <c r="T7">
-        <f t="shared" si="2"/>
-        <v>181</v>
+        <f t="shared" si="0"/>
+        <v>169.72727272727272</v>
       </c>
       <c r="U7">
-        <f t="shared" si="3"/>
-        <v>0.33162857142857144</v>
+        <f t="shared" si="0"/>
+        <v>0.33005454545454543</v>
       </c>
       <c r="V7">
-        <f t="shared" si="1"/>
-        <v>0.43935714285714284</v>
+        <f t="shared" si="0"/>
+        <v>0.4368636363636364</v>
       </c>
       <c r="W7">
-        <f t="shared" si="1"/>
-        <v>1495</v>
+        <f t="shared" si="0"/>
+        <v>1509.1818181818182</v>
       </c>
       <c r="X7">
-        <f t="shared" si="1"/>
-        <v>104.85714285714286</v>
+        <f t="shared" si="0"/>
+        <v>102.36363636363636</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="1"/>
-        <v>3.6807142857142852</v>
+        <f t="shared" si="0"/>
+        <v>3.6986363636363637</v>
       </c>
       <c r="Z7">
-        <f t="shared" si="1"/>
-        <v>1.1805714285714288</v>
+        <f t="shared" si="0"/>
+        <v>1.1894545454545455</v>
       </c>
       <c r="AA7">
-        <f t="shared" si="1"/>
-        <v>3.3711428571428574</v>
+        <f t="shared" si="0"/>
+        <v>3.2961818181818177</v>
       </c>
       <c r="AB7">
-        <f t="shared" si="1"/>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>105.54545454545455</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1702,55 +1750,55 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>1003.1428571428571</v>
+        <f t="shared" si="1"/>
+        <v>1005.6363636363636</v>
       </c>
       <c r="R8">
-        <f t="shared" si="0"/>
-        <v>286.28571428571428</v>
+        <f t="shared" si="2"/>
+        <v>283.63636363636363</v>
       </c>
       <c r="S8">
         <f t="shared" si="0"/>
-        <v>973.42857142857144</v>
+        <v>964.5454545454545</v>
       </c>
       <c r="T8">
-        <f t="shared" si="2"/>
-        <v>168.8</v>
+        <f t="shared" si="0"/>
+        <v>158.81818181818181</v>
       </c>
       <c r="U8">
-        <f t="shared" si="3"/>
-        <v>0.3293571428571429</v>
+        <f t="shared" si="0"/>
+        <v>0.32835454545454551</v>
       </c>
       <c r="V8">
-        <f t="shared" si="1"/>
-        <v>0.4329142857142857</v>
+        <f t="shared" si="0"/>
+        <v>0.43258181818181818</v>
       </c>
       <c r="W8">
-        <f t="shared" si="1"/>
-        <v>1449.5714285714287</v>
+        <f t="shared" si="0"/>
+        <v>1469.3636363636363</v>
       </c>
       <c r="X8">
-        <f t="shared" si="1"/>
-        <v>102.71428571428571</v>
+        <f t="shared" si="0"/>
+        <v>100.63636363636364</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="1"/>
-        <v>3.7528571428571427</v>
+        <f t="shared" si="0"/>
+        <v>3.7463636363636366</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="1"/>
-        <v>1.1922857142857144</v>
+        <f t="shared" si="0"/>
+        <v>1.1998181818181819</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="1"/>
-        <v>3.2961428571428573</v>
+        <f t="shared" si="0"/>
+        <v>3.2404545454545453</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="1"/>
-        <v>97.857142857142861</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>101.54545454545455</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1794,55 +1842,55 @@
         <v>7</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>990.71428571428567</v>
+        <f t="shared" si="1"/>
+        <v>997</v>
       </c>
       <c r="R9">
-        <f t="shared" si="0"/>
-        <v>280.57142857142856</v>
+        <f t="shared" si="2"/>
+        <v>274.54545454545456</v>
       </c>
       <c r="S9">
         <f t="shared" si="0"/>
-        <v>962.28571428571433</v>
+        <v>955.63636363636363</v>
       </c>
       <c r="T9">
-        <f t="shared" si="2"/>
-        <v>156.80000000000001</v>
+        <f t="shared" si="0"/>
+        <v>148.90909090909091</v>
       </c>
       <c r="U9">
-        <f t="shared" si="3"/>
-        <v>0.32681428571428572</v>
+        <f t="shared" si="0"/>
+        <v>0.32626363636363637</v>
       </c>
       <c r="V9">
-        <f t="shared" si="1"/>
-        <v>0.43064285714285716</v>
+        <f t="shared" si="0"/>
+        <v>0.43073636363636364</v>
       </c>
       <c r="W9">
-        <f t="shared" si="1"/>
-        <v>1427.7142857142858</v>
+        <f t="shared" si="0"/>
+        <v>1436.909090909091</v>
       </c>
       <c r="X9">
-        <f t="shared" si="1"/>
-        <v>97.714285714285708</v>
+        <f t="shared" si="0"/>
+        <v>96.36363636363636</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="1"/>
-        <v>3.8565714285714283</v>
+        <f t="shared" si="0"/>
+        <v>3.8152727272727276</v>
       </c>
       <c r="Z9">
-        <f t="shared" si="1"/>
-        <v>1.2042857142857142</v>
+        <f t="shared" si="0"/>
+        <v>1.2096363636363636</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="1"/>
-        <v>3.2169999999999996</v>
+        <f t="shared" si="0"/>
+        <v>3.1755454545454551</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="1"/>
-        <v>95.142857142857139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1886,55 +1934,55 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="0"/>
-        <v>985.57142857142856</v>
+        <f t="shared" si="1"/>
+        <v>976.63636363636363</v>
       </c>
       <c r="R10">
-        <f t="shared" si="0"/>
-        <v>267.57142857142856</v>
+        <f t="shared" si="2"/>
+        <v>265.90909090909093</v>
       </c>
       <c r="S10">
         <f t="shared" si="0"/>
-        <v>957.28571428571433</v>
+        <v>939.36363636363637</v>
       </c>
       <c r="T10">
-        <f t="shared" si="2"/>
-        <v>142.80000000000001</v>
+        <f t="shared" si="0"/>
+        <v>140.54545454545453</v>
       </c>
       <c r="U10">
-        <f t="shared" si="3"/>
-        <v>0.32514285714285712</v>
+        <f t="shared" si="0"/>
+        <v>0.32465454545454542</v>
       </c>
       <c r="V10">
-        <f t="shared" si="1"/>
-        <v>0.42881428571428565</v>
+        <f t="shared" si="0"/>
+        <v>0.42949999999999999</v>
       </c>
       <c r="W10">
-        <f t="shared" si="1"/>
-        <v>1364.5714285714287</v>
+        <f t="shared" si="0"/>
+        <v>1386.1818181818182</v>
       </c>
       <c r="X10">
-        <f t="shared" si="1"/>
-        <v>90.428571428571431</v>
+        <f t="shared" si="0"/>
+        <v>91</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="1"/>
-        <v>4.0117142857142856</v>
+        <f t="shared" si="0"/>
+        <v>3.923090909090909</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="1"/>
-        <v>1.2215714285714285</v>
+        <f t="shared" si="0"/>
+        <v>1.2217272727272728</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="1"/>
-        <v>3.157285714285714</v>
+        <f t="shared" si="0"/>
+        <v>3.0986363636363632</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="1"/>
-        <v>84.285714285714292</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>85.272727272727266</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1978,55 +2026,55 @@
         <v>9</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="0"/>
-        <v>967</v>
+        <f t="shared" si="1"/>
+        <v>953.90909090909088</v>
       </c>
       <c r="R11">
-        <f t="shared" si="0"/>
-        <v>260.42857142857144</v>
+        <f t="shared" si="2"/>
+        <v>260.63636363636363</v>
       </c>
       <c r="S11">
         <f t="shared" si="0"/>
-        <v>929.85714285714289</v>
+        <v>918.63636363636363</v>
       </c>
       <c r="T11">
-        <f t="shared" si="2"/>
-        <v>137.19999999999999</v>
+        <f t="shared" si="0"/>
+        <v>131</v>
       </c>
       <c r="U11">
-        <f t="shared" si="3"/>
-        <v>0.32221428571428568</v>
+        <f t="shared" si="0"/>
+        <v>0.32242727272727273</v>
       </c>
       <c r="V11">
-        <f t="shared" si="1"/>
-        <v>0.42661428571428578</v>
+        <f t="shared" si="0"/>
+        <v>0.42624545454545454</v>
       </c>
       <c r="W11">
-        <f t="shared" si="1"/>
-        <v>1311.2857142857142</v>
+        <f t="shared" si="0"/>
+        <v>1263.909090909091</v>
       </c>
       <c r="X11">
-        <f t="shared" si="1"/>
-        <v>86.714285714285708</v>
+        <f t="shared" si="0"/>
+        <v>88.272727272727266</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="1"/>
-        <v>4.0638571428571435</v>
+        <f t="shared" si="0"/>
+        <v>3.9922727272727272</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="1"/>
-        <v>1.2547142857142857</v>
+        <f t="shared" si="0"/>
+        <v>1.2450000000000001</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="1"/>
-        <v>3.0467142857142853</v>
+        <f t="shared" si="0"/>
+        <v>3.019545454545455</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="1"/>
-        <v>75.714285714285708</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>77.63636363636364</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2070,55 +2118,55 @@
         <v>10</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="0"/>
-        <v>958.14285714285711</v>
+        <f t="shared" si="1"/>
+        <v>943.18181818181813</v>
       </c>
       <c r="R12">
-        <f t="shared" si="0"/>
-        <v>256.14285714285717</v>
+        <f t="shared" si="2"/>
+        <v>257.18181818181819</v>
       </c>
       <c r="S12">
         <f t="shared" si="0"/>
-        <v>915.28571428571433</v>
+        <v>906.4545454545455</v>
       </c>
       <c r="T12">
-        <f t="shared" si="2"/>
-        <v>125.4</v>
+        <f t="shared" si="0"/>
+        <v>114.54545454545455</v>
       </c>
       <c r="U12">
-        <f t="shared" si="3"/>
-        <v>0.32072857142857142</v>
+        <f t="shared" si="0"/>
+        <v>0.32144545454545453</v>
       </c>
       <c r="V12">
-        <f t="shared" si="1"/>
-        <v>0.42379999999999995</v>
+        <f t="shared" si="0"/>
+        <v>0.42245454545454542</v>
       </c>
       <c r="W12">
-        <f t="shared" si="1"/>
-        <v>1259.7142857142858</v>
+        <f t="shared" si="0"/>
+        <v>1227.4545454545455</v>
       </c>
       <c r="X12">
-        <f t="shared" si="1"/>
-        <v>82.571428571428569</v>
+        <f t="shared" si="0"/>
+        <v>81.63636363636364</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="1"/>
-        <v>4.1384285714285713</v>
+        <f t="shared" si="0"/>
+        <v>4.1237272727272725</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="1"/>
-        <v>1.2617142857142858</v>
+        <f t="shared" si="0"/>
+        <v>1.2538181818181817</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="1"/>
-        <v>2.9858571428571428</v>
+        <f t="shared" si="0"/>
+        <v>2.9342727272727274</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="1"/>
-        <v>69.142857142857139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>73.454545454545453</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2162,55 +2210,55 @@
         <v>11</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="0"/>
-        <v>928</v>
+        <f t="shared" si="1"/>
+        <v>913.81818181818187</v>
       </c>
       <c r="R13">
-        <f t="shared" si="0"/>
-        <v>251.14285714285714</v>
+        <f t="shared" si="2"/>
+        <v>253.27272727272728</v>
       </c>
       <c r="S13">
         <f t="shared" si="0"/>
-        <v>878.42857142857144</v>
+        <v>870.27272727272725</v>
       </c>
       <c r="T13">
-        <f t="shared" si="2"/>
-        <v>115</v>
+        <f t="shared" si="0"/>
+        <v>101.72727272727273</v>
       </c>
       <c r="U13">
-        <f t="shared" si="3"/>
-        <v>0.31890000000000002</v>
+        <f t="shared" si="0"/>
+        <v>0.3194818181818182</v>
       </c>
       <c r="V13">
-        <f t="shared" si="1"/>
-        <v>0.41884285714285718</v>
+        <f t="shared" si="0"/>
+        <v>0.41653636363636365</v>
       </c>
       <c r="W13">
-        <f t="shared" si="1"/>
-        <v>1197.7142857142858</v>
+        <f t="shared" si="0"/>
+        <v>1179.6363636363637</v>
       </c>
       <c r="X13">
-        <f t="shared" si="1"/>
-        <v>69.714285714285708</v>
+        <f t="shared" si="0"/>
+        <v>67.272727272727266</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="1"/>
-        <v>4.1912857142857138</v>
+        <f t="shared" si="0"/>
+        <v>4.173</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="1"/>
-        <v>1.2647142857142857</v>
+        <f t="shared" si="0"/>
+        <v>1.2575454545454545</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="1"/>
-        <v>2.8477142857142854</v>
+        <f t="shared" si="0"/>
+        <v>2.8143636363636362</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="1"/>
-        <v>56.142857142857146</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>64.090909090909093</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2254,155 +2302,155 @@
         <v>12</v>
       </c>
       <c r="Q14">
-        <f>(3*B77+2*B14+B30+B46)/7</f>
-        <v>903.57142857142856</v>
+        <f t="shared" si="1"/>
+        <v>884.81818181818187</v>
       </c>
       <c r="R14">
-        <f t="shared" si="0"/>
-        <v>226</v>
+        <f t="shared" si="2"/>
+        <v>212.18181818181819</v>
       </c>
       <c r="S14">
         <f t="shared" si="0"/>
-        <v>842.57142857142856</v>
+        <v>818.36363636363637</v>
       </c>
       <c r="T14">
-        <f t="shared" si="2"/>
-        <v>90.2</v>
+        <f t="shared" si="0"/>
+        <v>75.727272727272734</v>
       </c>
       <c r="U14">
+        <f t="shared" si="0"/>
+        <v>0.3146272727272727</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="0"/>
+        <v>0.41210000000000002</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="0"/>
+        <v>978.63636363636363</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="0"/>
+        <v>49.636363636363633</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="0"/>
+        <v>4.3376363636363635</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="0"/>
+        <v>1.2714545454545456</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="0"/>
+        <v>2.636181818181818</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f t="shared" ref="B15:M15" si="3">-1*SLOPE(B4:B13,$A$4:$A$13)</f>
+        <v>11.406060606060606</v>
+      </c>
+      <c r="C15">
         <f t="shared" si="3"/>
-        <v>0.31578571428571423</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="1"/>
-        <v>0.41289999999999999</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="1"/>
-        <v>987.57142857142856</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="1"/>
-        <v>53.428571428571431</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="1"/>
-        <v>4.3785714285714281</v>
-      </c>
-      <c r="Z14">
-        <f t="shared" si="1"/>
-        <v>1.2785714285714285</v>
-      </c>
-      <c r="AA14">
-        <f t="shared" si="1"/>
-        <v>2.6562857142857146</v>
-      </c>
-      <c r="AB14">
-        <f t="shared" si="1"/>
-        <v>41.142857142857146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <f t="shared" ref="B15:M15" si="4">-1*SLOPE(B4:B13,$A$4:$A$13)</f>
-        <v>11.406060606060606</v>
-      </c>
-      <c r="C15">
+        <v>5.9333333333333336</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="3"/>
+        <v>14.393939393939394</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="3"/>
+        <v>9.2242424242424246</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="3"/>
+        <v>1.6048484848484807E-3</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="3"/>
+        <v>2.6684848484848506E-3</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="3"/>
+        <v>49.460606060606061</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="3"/>
+        <v>4.3939393939393936</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>-7.7290909090909091E-2</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="3"/>
+        <v>-1.0775757575757577E-2</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>7.3684848484848478E-2</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="3"/>
+        <v>6.1515151515151514</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f t="shared" ref="B16:G16" si="4">B15/$D$15</f>
+        <v>0.79242105263157891</v>
+      </c>
+      <c r="C16">
         <f t="shared" si="4"/>
-        <v>5.9333333333333336</v>
-      </c>
-      <c r="D15">
+        <v>0.41221052631578947</v>
+      </c>
+      <c r="D16">
         <f t="shared" si="4"/>
-        <v>14.393939393939394</v>
-      </c>
-      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="E16">
         <f t="shared" si="4"/>
-        <v>9.2242424242424246</v>
-      </c>
-      <c r="F15">
+        <v>0.64084210526315788</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="4"/>
-        <v>1.6048484848484807E-3</v>
-      </c>
-      <c r="G15">
+        <v>1.1149473684210496E-4</v>
+      </c>
+      <c r="G16">
         <f t="shared" si="4"/>
-        <v>2.6684848484848506E-3</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="4"/>
-        <v>49.460606060606061</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="4"/>
-        <v>4.3939393939393936</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="4"/>
-        <v>-7.7290909090909091E-2</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="4"/>
-        <v>-1.0775757575757577E-2</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="4"/>
-        <v>7.3684848484848478E-2</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="4"/>
-        <v>6.1515151515151514</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B16">
-        <f t="shared" ref="B16:G16" si="5">B15/$D$15</f>
-        <v>0.79242105263157891</v>
-      </c>
-      <c r="C16">
+        <v>1.8538947368421067E-4</v>
+      </c>
+      <c r="H16">
+        <f t="shared" ref="H16:M16" si="5">H15/$H$15</f>
+        <v>1</v>
+      </c>
+      <c r="I16">
         <f t="shared" si="5"/>
-        <v>0.41221052631578947</v>
-      </c>
-      <c r="D16">
+        <v>8.8837152309765952E-2</v>
+      </c>
+      <c r="J16">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E16">
+        <v>-1.5626761426295796E-3</v>
+      </c>
+      <c r="K16">
         <f t="shared" si="5"/>
-        <v>0.64084210526315788</v>
-      </c>
-      <c r="F16">
+        <v>-2.1786545766450192E-4</v>
+      </c>
+      <c r="L16">
         <f t="shared" si="5"/>
-        <v>1.1149473684210496E-4</v>
-      </c>
-      <c r="G16">
+        <v>1.4897684107339786E-3</v>
+      </c>
+      <c r="M16">
         <f t="shared" si="5"/>
-        <v>1.8538947368421067E-4</v>
-      </c>
-      <c r="H16">
-        <f t="shared" ref="H16:M16" si="6">H15/$H$15</f>
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="6"/>
-        <v>8.8837152309765952E-2</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="6"/>
-        <v>-1.5626761426295796E-3</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="6"/>
-        <v>-2.1786545766450192E-4</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="6"/>
-        <v>1.4897684107339786E-3</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="6"/>
         <v>0.12437201323367233</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2022</v>
       </c>
@@ -2410,55 +2458,55 @@
         <v>14</v>
       </c>
       <c r="Q17">
-        <f t="shared" ref="Q17:AB17" si="7">AVERAGE(Q3:Q14)</f>
-        <v>1002.9285714285714</v>
+        <f t="shared" ref="Q17:AB17" si="6">AVERAGE(Q3:Q14)</f>
+        <v>993.77272727272714</v>
       </c>
       <c r="R17">
-        <f t="shared" si="7"/>
-        <v>281.25000000000006</v>
+        <f t="shared" si="6"/>
+        <v>279.280303030303</v>
       </c>
       <c r="S17">
-        <f t="shared" si="7"/>
-        <v>965.86904761904759</v>
+        <f t="shared" si="6"/>
+        <v>956.88636363636363</v>
       </c>
       <c r="T17">
-        <f t="shared" si="7"/>
-        <v>166.01666666666668</v>
+        <f t="shared" si="6"/>
+        <v>153.09848484848484</v>
       </c>
       <c r="U17">
-        <f t="shared" si="7"/>
-        <v>0.3281297619047619</v>
+        <f t="shared" si="6"/>
+        <v>0.32766136363636361</v>
       </c>
       <c r="V17">
-        <f t="shared" si="7"/>
-        <v>0.43445238095238087</v>
+        <f t="shared" si="6"/>
+        <v>0.43352121212121203</v>
       </c>
       <c r="W17">
-        <f t="shared" si="7"/>
-        <v>1444.7380952380954</v>
+        <f t="shared" si="6"/>
+        <v>1434.4090909090908</v>
       </c>
       <c r="X17">
-        <f t="shared" si="7"/>
-        <v>98.047619047619037</v>
+        <f t="shared" si="6"/>
+        <v>95.727272727272734</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="7"/>
-        <v>3.8374642857142853</v>
+        <f t="shared" si="6"/>
+        <v>3.8285075757575764</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="7"/>
-        <v>1.2040714285714285</v>
+        <f t="shared" si="6"/>
+        <v>1.2065000000000001</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="7"/>
-        <v>3.2813214285714278</v>
+        <f t="shared" si="6"/>
+        <v>3.2234166666666666</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="7"/>
-        <v>92.714285714285708</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>95.424242424242422</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -2500,54 +2548,54 @@
       </c>
       <c r="Q18">
         <f>Q17/13</f>
-        <v>77.14835164835165</v>
+        <v>76.444055944055933</v>
       </c>
       <c r="R18">
         <f>R17/13</f>
-        <v>21.63461538461539</v>
+        <v>21.483100233100231</v>
       </c>
       <c r="S18">
         <f>S17/13</f>
-        <v>74.297619047619051</v>
+        <v>73.60664335664336</v>
       </c>
       <c r="T18">
         <f>T17/13</f>
-        <v>12.770512820512822</v>
+        <v>11.776806526806526</v>
       </c>
       <c r="U18">
         <f>U17</f>
-        <v>0.3281297619047619</v>
+        <v>0.32766136363636361</v>
       </c>
       <c r="V18">
         <f>V17</f>
-        <v>0.43445238095238087</v>
+        <v>0.43352121212121203</v>
       </c>
       <c r="W18">
         <f>W17/9</f>
-        <v>160.52645502645504</v>
+        <v>159.37878787878788</v>
       </c>
       <c r="X18">
         <f>X17/9</f>
-        <v>10.894179894179892</v>
+        <v>10.636363636363637</v>
       </c>
       <c r="Y18">
         <f>Y17</f>
-        <v>3.8374642857142853</v>
+        <v>3.8285075757575764</v>
       </c>
       <c r="Z18">
         <f>Z17</f>
-        <v>1.2040714285714285</v>
+        <v>1.2065000000000001</v>
       </c>
       <c r="AA18">
         <f>AA17</f>
-        <v>3.2813214285714278</v>
+        <v>3.2234166666666666</v>
       </c>
       <c r="AB18">
         <f>AB17/9</f>
-        <v>10.301587301587301</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+        <v>10.602693602693602</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1</v>
       </c>
@@ -2591,55 +2639,55 @@
         <v>16</v>
       </c>
       <c r="Q19">
-        <f t="shared" ref="Q19:AB19" si="8">_xlfn.STDEV.P(Q3:Q14)</f>
-        <v>56.25843852047359</v>
+        <f t="shared" ref="Q19:AB19" si="7">_xlfn.STDEV.P(Q3:Q14)</f>
+        <v>58.08677725145418</v>
       </c>
       <c r="R19">
-        <f t="shared" si="8"/>
-        <v>29.345996319770116</v>
+        <f t="shared" si="7"/>
+        <v>31.629145343652343</v>
       </c>
       <c r="S19">
-        <f t="shared" si="8"/>
-        <v>64.517715183989253</v>
+        <f t="shared" si="7"/>
+        <v>69.264834166163382</v>
       </c>
       <c r="T19">
-        <f t="shared" si="8"/>
-        <v>44.550529988118122</v>
+        <f t="shared" si="7"/>
+        <v>41.083893513690448</v>
       </c>
       <c r="U19">
-        <f t="shared" si="8"/>
-        <v>7.5801509918310426E-3</v>
+        <f t="shared" si="7"/>
+        <v>7.4824745882754217E-3</v>
       </c>
       <c r="V19">
-        <f t="shared" si="8"/>
-        <v>1.3350667303933446E-2</v>
+        <f t="shared" si="7"/>
+        <v>1.3287797242415867E-2</v>
       </c>
       <c r="W19">
-        <f t="shared" si="8"/>
-        <v>233.72207777013224</v>
+        <f t="shared" si="7"/>
+        <v>231.34566668324038</v>
       </c>
       <c r="X19">
-        <f t="shared" si="8"/>
-        <v>22.584936685307913</v>
+        <f t="shared" si="7"/>
+        <v>21.593987021439403</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="8"/>
-        <v>0.30717095732475991</v>
+        <f t="shared" si="7"/>
+        <v>0.27786383702468181</v>
       </c>
       <c r="Z19">
-        <f t="shared" si="8"/>
-        <v>5.0614506135025293E-2</v>
+        <f t="shared" si="7"/>
+        <v>4.3491576398549343E-2</v>
       </c>
       <c r="AA19">
-        <f t="shared" si="8"/>
-        <v>0.35901897759799828</v>
+        <f t="shared" si="7"/>
+        <v>0.3420564016336059</v>
       </c>
       <c r="AB19">
-        <f t="shared" si="8"/>
-        <v>28.089567627925675</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v>24.411145823251395</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2683,55 +2731,55 @@
         <v>17</v>
       </c>
       <c r="Q20">
-        <f t="shared" ref="Q20:AB20" si="9">MEDIAN(Q3:Q14)</f>
-        <v>996.92857142857133</v>
+        <f t="shared" ref="Q20:AB20" si="8">MEDIAN(Q3:Q14)</f>
+        <v>1001.3181818181818</v>
       </c>
       <c r="R20">
-        <f t="shared" si="9"/>
-        <v>283.42857142857144</v>
+        <f t="shared" si="8"/>
+        <v>279.09090909090912</v>
       </c>
       <c r="S20">
-        <f t="shared" si="9"/>
-        <v>967.85714285714289</v>
+        <f t="shared" si="8"/>
+        <v>960.09090909090901</v>
       </c>
       <c r="T20">
-        <f t="shared" si="9"/>
-        <v>162.80000000000001</v>
+        <f t="shared" si="8"/>
+        <v>153.86363636363637</v>
       </c>
       <c r="U20">
-        <f t="shared" si="9"/>
-        <v>0.32808571428571431</v>
+        <f t="shared" si="8"/>
+        <v>0.32730909090909094</v>
       </c>
       <c r="V20">
-        <f t="shared" si="9"/>
-        <v>0.43177857142857146</v>
+        <f t="shared" si="8"/>
+        <v>0.43165909090909094</v>
       </c>
       <c r="W20">
-        <f t="shared" si="9"/>
-        <v>1438.6428571428573</v>
+        <f t="shared" si="8"/>
+        <v>1453.1363636363635</v>
       </c>
       <c r="X20">
-        <f t="shared" si="9"/>
-        <v>100.21428571428571</v>
+        <f t="shared" si="8"/>
+        <v>98.5</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="9"/>
-        <v>3.8047142857142857</v>
+        <f t="shared" si="8"/>
+        <v>3.7808181818181819</v>
       </c>
       <c r="Z20">
-        <f t="shared" si="9"/>
-        <v>1.1982857142857144</v>
+        <f t="shared" si="8"/>
+        <v>1.2047272727272729</v>
       </c>
       <c r="AA20">
-        <f t="shared" si="9"/>
-        <v>3.2565714285714282</v>
+        <f t="shared" si="8"/>
+        <v>3.2080000000000002</v>
       </c>
       <c r="AB20">
-        <f t="shared" si="9"/>
-        <v>96.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>99.77272727272728</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3</v>
       </c>
@@ -2775,55 +2823,55 @@
         <v>18</v>
       </c>
       <c r="Q21">
-        <f t="shared" ref="Q21:AB21" si="10">_xlfn.VAR.P(Q3:Q14)</f>
-        <v>3165.0119047619069</v>
+        <f t="shared" ref="Q21:AB21" si="9">_xlfn.VAR.P(Q3:Q14)</f>
+        <v>3374.0736914600548</v>
       </c>
       <c r="R21">
-        <f t="shared" si="10"/>
-        <v>861.18749999996123</v>
+        <f t="shared" si="9"/>
+        <v>1000.4028351698847</v>
       </c>
       <c r="S21">
-        <f t="shared" si="10"/>
-        <v>4162.5355725623567</v>
+        <f t="shared" si="9"/>
+        <v>4797.6172520661139</v>
       </c>
       <c r="T21">
-        <f t="shared" si="10"/>
-        <v>1984.7497222222123</v>
+        <f t="shared" si="9"/>
+        <v>1687.8863062442558</v>
       </c>
       <c r="U21">
-        <f t="shared" si="10"/>
-        <v>5.7458689058957135E-5</v>
+        <f t="shared" si="9"/>
+        <v>5.5987425964187443E-5</v>
       </c>
       <c r="V21">
-        <f t="shared" si="10"/>
-        <v>1.7824031746031756E-4</v>
+        <f t="shared" si="9"/>
+        <v>1.7656555555555471E-4</v>
       </c>
       <c r="W21">
-        <f t="shared" si="10"/>
-        <v>54626.009637187752</v>
+        <f t="shared" si="9"/>
+        <v>53520.817493112962</v>
       </c>
       <c r="X21">
-        <f t="shared" si="10"/>
-        <v>510.07936507936716</v>
+        <f t="shared" si="9"/>
+        <v>466.30027548209341</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="10"/>
-        <v>9.4353997023809463E-2</v>
+        <f t="shared" si="9"/>
+        <v>7.7208311926078924E-2</v>
       </c>
       <c r="Z21">
-        <f t="shared" si="10"/>
-        <v>2.5618282312925133E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.8915172176308542E-3</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="10"/>
-        <v>0.12889462627551199</v>
+        <f t="shared" si="9"/>
+        <v>0.11700258189853072</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="10"/>
-        <v>789.02380952380997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v>595.90404040404405</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>4</v>
       </c>
@@ -2865,7 +2913,7 @@
       </c>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>5</v>
       </c>
@@ -2915,7 +2963,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6</v>
       </c>
@@ -2966,21 +3014,21 @@
       </c>
       <c r="W24" s="5">
         <f>(12*SLOPE(W4:W13,$P$4:$P$13)+INTERCEPT(W4:W13,$P$4:$P$13))/12</f>
-        <v>94.228571428571442</v>
+        <v>92.818181818181827</v>
       </c>
       <c r="X24" s="5">
         <f>(12*SLOPE(X4:X13,$P$4:$P$13)+INTERCEPT(X4:X13,$P$4:$P$13))/9</f>
-        <v>7.663492063492062</v>
+        <v>7.7131313131313117</v>
       </c>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
       <c r="AA24" s="5"/>
       <c r="AB24" s="5">
         <f>(12*SLOPE(AB4:AB13,$P$4:$P$13)+INTERCEPT(AB4:AB13,$P$4:$P$13))/3</f>
-        <v>18.377777777777769</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20.131313131313135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>7</v>
       </c>
@@ -3027,7 +3075,7 @@
         <v>9.2242424242424246</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>8</v>
       </c>
@@ -3072,54 +3120,54 @@
       </c>
       <c r="Q26" s="7">
         <f>(12*SLOPE(Q4:Q13,$P$4:$P$13)+INTERCEPT(Q4:Q13,$P$4:$P$13))/13</f>
-        <v>70.609523809523807</v>
+        <v>69.793006993007012</v>
       </c>
       <c r="R26" s="7">
         <f>(12*SLOPE(R4:R13,$P$4:$P$13)+INTERCEPT(R4:R13,$P$4:$P$13))/13</f>
-        <v>18.566300366300368</v>
+        <v>18.550582750582752</v>
       </c>
       <c r="S26" s="7">
         <f>(12*SLOPE(S4:S13,$P$4:$P$13)+INTERCEPT(S4:S13,$P$4:$P$13))/13</f>
-        <v>67.730402930402946</v>
+        <v>66.730069930069945</v>
       </c>
       <c r="T26" s="7">
         <f>(12*SLOPE(T4:T13,$P$4:$P$13)+INTERCEPT(T4:T13,$P$4:$P$13))/13</f>
-        <v>7.509743589743592</v>
+        <v>7.1776223776223782</v>
       </c>
       <c r="U26" s="7">
         <f>(12*SLOPE(U4:U13,$P$4:$P$13)+INTERCEPT(U4:U13,$P$4:$P$13))</f>
-        <v>0.3165885714285715</v>
+        <v>0.31711878787878778</v>
       </c>
       <c r="V26" s="7">
         <f>(12*SLOPE(V4:V13,$P$4:$P$13)+INTERCEPT(V4:V13,$P$4:$P$13))</f>
-        <v>0.41529809523809524</v>
+        <v>0.41469272727272727</v>
       </c>
       <c r="W26" s="7">
         <f>(12*SLOPE(W4:W13,$P$4:$P$13)+INTERCEPT(W4:W13,$P$4:$P$13))/12</f>
-        <v>94.228571428571442</v>
+        <v>92.818181818181827</v>
       </c>
       <c r="X26" s="7">
         <f>(12*SLOPE(X4:X13,$P$4:$P$13)+INTERCEPT(X4:X13,$P$4:$P$13))/9</f>
-        <v>7.663492063492062</v>
+        <v>7.7131313131313117</v>
       </c>
       <c r="Y26" s="7">
         <f>(12*SLOPE(Y4:Y13,$P$4:$P$13)+INTERCEPT(Y4:Y13,$P$4:$P$13))</f>
-        <v>4.3037047619047613</v>
+        <v>4.2237151515151519</v>
       </c>
       <c r="Z26" s="7">
         <f>(12*SLOPE(Z4:Z13,$P$4:$P$13)+INTERCEPT(Z4:Z13,$P$4:$P$13))</f>
-        <v>1.2834761904761904</v>
+        <v>1.2728787878787879</v>
       </c>
       <c r="AA26" s="7">
         <f>(12*SLOPE(AA4:AA13,$P$4:$P$13)+INTERCEPT(AA4:AA13,$P$4:$P$13))</f>
-        <v>2.7619619047619035</v>
+        <v>2.7432848484848491</v>
       </c>
       <c r="AB26" s="7">
         <f>(12*SLOPE(AB4:AB13,$P$4:$P$13)+INTERCEPT(AB4:AB13,$P$4:$P$13))/3</f>
-        <v>18.377777777777769</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>20.131313131313135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>9</v>
       </c>
@@ -3163,55 +3211,55 @@
         <v>23</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" ref="Q27:AB27" si="11">-1*SLOPE(Q4:Q13,$P$4:$P$13)</f>
-        <v>15.683982683982686</v>
+        <f t="shared" ref="Q27:AB27" si="10">-1*SLOPE(Q4:Q13,$P$4:$P$13)</f>
+        <v>16.226446280991738</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="11"/>
-        <v>7.2874458874458883</v>
+        <f t="shared" si="10"/>
+        <v>7.1366391184572988</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="11"/>
-        <v>15.613852813852809</v>
+        <f t="shared" si="10"/>
+        <v>16.505785123966938</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="11"/>
-        <v>12.555151515151515</v>
+        <f t="shared" si="10"/>
+        <v>11.130578512396696</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="11"/>
-        <v>2.0805194805194839E-3</v>
+        <f t="shared" si="10"/>
+        <v>1.8967493112947687E-3</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="11"/>
-        <v>3.3972294372294379E-3</v>
+        <f t="shared" si="10"/>
+        <v>3.3226446280991695E-3</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="11"/>
-        <v>58.067532467532466</v>
+        <f t="shared" si="10"/>
+        <v>59.920661157024789</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="11"/>
-        <v>5.3454545454545466</v>
+        <f t="shared" si="10"/>
+        <v>4.9553719008264467</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="11"/>
-        <v>-8.6045021645021633E-2</v>
+        <f t="shared" si="10"/>
+        <v>-7.2483746556473813E-2</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="11"/>
-        <v>-1.4143722943722932E-2</v>
+        <f t="shared" si="10"/>
+        <v>-1.1739944903581261E-2</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="11"/>
-        <v>9.4032900432900468E-2</v>
+        <f t="shared" si="10"/>
+        <v>8.5868870523415963E-2</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="11"/>
-        <v>6.7887445887445885</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>6.3763085399449029</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>10</v>
       </c>
@@ -3256,11 +3304,11 @@
       </c>
       <c r="Q28" s="11">
         <f>$S$27/Q27</f>
-        <v>0.99552856748550878</v>
+        <v>1.0172150351431186</v>
       </c>
       <c r="R28" s="11">
         <f>$S$27/R27</f>
-        <v>2.142568611144112</v>
+        <v>2.3128232841812704</v>
       </c>
       <c r="S28" s="11">
         <f>$S$27/S27</f>
@@ -3268,42 +3316,42 @@
       </c>
       <c r="T28" s="11">
         <f>$S$27/T27</f>
-        <v>1.243621217554409</v>
+        <v>1.4829224829224823</v>
       </c>
       <c r="U28" s="11">
         <f>$S$27/U27/1000</f>
-        <v>7.5047856845609511</v>
+        <v>8.702143728577223</v>
       </c>
       <c r="V28" s="11">
         <f>$S$27/V27/1000</f>
-        <v>4.5960548447933105</v>
+        <v>4.967664908964287</v>
       </c>
       <c r="W28" s="11">
-        <f t="shared" ref="W28:AB28" si="12">W27/$W$27</f>
+        <f t="shared" ref="W28:AB28" si="11">W27/$W$27</f>
         <v>1</v>
       </c>
       <c r="X28" s="11">
-        <f t="shared" si="12"/>
-        <v>9.2055823939881931E-2</v>
+        <f t="shared" si="11"/>
+        <v>8.2698885578726705E-2</v>
       </c>
       <c r="Y28" s="11">
-        <f t="shared" si="12"/>
-        <v>-1.4818095067692489E-3</v>
+        <f t="shared" si="11"/>
+        <v>-1.2096619956600094E-3</v>
       </c>
       <c r="Z28" s="11">
-        <f t="shared" si="12"/>
-        <v>-2.435736864078247E-4</v>
+        <f t="shared" si="11"/>
+        <v>-1.9592482253852651E-4</v>
       </c>
       <c r="AA28" s="11">
-        <f t="shared" si="12"/>
-        <v>1.6193713842667151E-3</v>
+        <f t="shared" si="11"/>
+        <v>1.4330427746515133E-3</v>
       </c>
       <c r="AB28" s="11">
-        <f t="shared" si="12"/>
-        <v>0.11691119460845709</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>0.10641251976902423</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>11</v>
       </c>
@@ -3344,7 +3392,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>12</v>
       </c>
@@ -3389,256 +3437,256 @@
       </c>
       <c r="Q30" s="13">
         <f>(IF(Q3&lt;Q45,Q3,Q4)-IF(Q14&gt;Q44,Q14,Q13))/(COUNT(IF(Q3&lt;Q45,Q3,Q4):IF(Q14&gt;Q44,Q14,Q13))-1)</f>
-        <v>16.922077922077928</v>
+        <v>17.280991735537192</v>
       </c>
       <c r="R30" s="13">
         <f>(IF(R3&lt;R45,R3,R4)-IF(R14&gt;R44,R14,R13))/(COUNT(IF(R3&lt;R45,R3,R4):IF(R14&gt;R44,R14,R13))-1)</f>
-        <v>9.870129870129869</v>
+        <v>7.616161616161615</v>
       </c>
       <c r="S30" s="13">
         <f>(IF(S3&lt;S45,S3,S4)-IF(S14&gt;S44,S14,S13))/(COUNT(IF(S3&lt;S45,S3,S4):IF(S14&gt;S44,S14,S13))-1)</f>
-        <v>21.961038961038959</v>
+        <v>21.127272727272725</v>
       </c>
       <c r="T30" s="13">
         <f>(IF(T3&lt;T45,T3,T4)-IF(T14&gt;T44,T14,T13))/(COUNT(IF(T3&lt;T45,T3,T4):IF(T14&gt;T44,T14,T13))-1)</f>
-        <v>13.181818181818182</v>
+        <v>12.768595041322312</v>
       </c>
       <c r="U30" s="13">
         <f>(IF(U3&lt;U45,U3,U4)-IF(U14&gt;U44,U14,U13))/(COUNT(IF(U3&lt;U45,U3,U4):IF(U14&gt;U44,U14,U13))-1)</f>
-        <v>2.3337662337662383E-3</v>
+        <v>2.4702479338842994E-3</v>
       </c>
       <c r="V30" s="13">
         <f>(IF(V3&lt;V45,V3,V4)-IF(V14&gt;V44,V14,V13))/(COUNT(IF(V3&lt;V45,V3,V4):IF(V14&gt;V44,V14,V13))-1)</f>
-        <v>4.0014285714285776E-3</v>
+        <v>3.7936363636363601E-3</v>
       </c>
       <c r="W30" s="13">
         <f>(IF(W3&lt;W45,W3,W4)-IF(W14&gt;W44,W14,W13))/(COUNT(IF(W3&lt;W45,W3,W4):IF(W14&gt;W44,W14,W13))-1)</f>
-        <v>65.04285714285713</v>
+        <v>74.710743801652896</v>
       </c>
       <c r="X30" s="13">
         <f>(IF(X3&lt;X45,X3,X4)-IF(X14&gt;X44,X14,X13))/(COUNT(IF(X3&lt;X45,X3,X4):IF(X14&gt;X44,X14,X13))-1)</f>
-        <v>6.1269841269841283</v>
+        <v>5.8383838383838382</v>
       </c>
       <c r="Y30" s="13">
         <f>(IF(Y3&lt;Y45,Y3,Y4)-IF(Y14&gt;Y44,Y14,Y13))/(COUNT(IF(Y3&lt;Y45,Y3,Y4):IF(Y14&gt;Y44,Y14,Y13))-1)</f>
-        <v>-9.2012987012986963E-2</v>
+        <v>-8.942975206611567E-2</v>
       </c>
       <c r="Z30" s="13">
         <f>(IF(Z3&lt;Z45,Z3,Z4)-IF(Z14&gt;Z44,Z14,Z13))/(COUNT(IF(Z3&lt;Z45,Z3,Z4):IF(Z14&gt;Z44,Z14,Z13))-1)</f>
-        <v>-1.5012987012987004E-2</v>
+        <v>-1.3454545454545467E-2</v>
       </c>
       <c r="AA30" s="13">
         <f>(IF(AA3&lt;AA45,AA3,AA4)-IF(AA14&gt;AA44,AA14,AA13))/(COUNT(IF(AA3&lt;AA45,AA3,AA4):IF(AA14&gt;AA44,AA14,AA13))-1)</f>
-        <v>0.11562337662337657</v>
+        <v>0.11390909090909092</v>
       </c>
       <c r="AB30" s="13">
         <f>(IF(AB3&lt;AB45,AB3,AB4)-IF(AB14&gt;AB44,AB14,AB13))/(COUNT(IF(AB3&lt;AB45,AB3,AB4):IF(AB14&gt;AB44,AB14,AB13))-1)</f>
-        <v>8.0142857142857142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+        <v>7.8595041322314065</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="B31">
-        <f t="shared" ref="B31:M31" si="13">-1*SLOPE(B20:B29,$A$20:$A$29)</f>
+        <f t="shared" ref="B31:M31" si="12">-1*SLOPE(B20:B29,$A$20:$A$29)</f>
         <v>10.32121212121212</v>
       </c>
       <c r="C31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>7</v>
       </c>
       <c r="D31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>19.163636363636364</v>
       </c>
       <c r="E31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>6.4969696969696971</v>
       </c>
       <c r="F31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2.8181818181818195E-3</v>
       </c>
       <c r="G31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2.621212121212121E-3</v>
       </c>
       <c r="H31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>68.442424242424238</v>
       </c>
       <c r="I31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>4.8909090909090907</v>
       </c>
       <c r="J31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-0.11393333333333333</v>
       </c>
       <c r="K31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-1.3939393939393944E-2</v>
       </c>
       <c r="L31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>7.4218181818181794E-2</v>
       </c>
       <c r="M31">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>10.109090909090909</v>
       </c>
       <c r="P31" s="12" t="s">
         <v>26</v>
       </c>
       <c r="Q31" s="13">
-        <f t="shared" ref="Q31:AB31" si="14">(Q3-Q14)/11</f>
-        <v>16.922077922077928</v>
+        <f t="shared" ref="Q31:AB31" si="13">(Q3-Q14)/11</f>
+        <v>17.280991735537192</v>
       </c>
       <c r="R31" s="13">
+        <f t="shared" si="13"/>
+        <v>11.173553719008261</v>
+      </c>
+      <c r="S31" s="13">
+        <f t="shared" si="13"/>
+        <v>23.925619834710741</v>
+      </c>
+      <c r="T31" s="13">
+        <f t="shared" si="13"/>
+        <v>12.768595041322312</v>
+      </c>
+      <c r="U31" s="13">
+        <f t="shared" si="13"/>
+        <v>2.4702479338842994E-3</v>
+      </c>
+      <c r="V31" s="13">
+        <f t="shared" si="13"/>
+        <v>4.3983471074380024E-3</v>
+      </c>
+      <c r="W31" s="13">
+        <f t="shared" si="13"/>
+        <v>74.710743801652896</v>
+      </c>
+      <c r="X31" s="13">
+        <f t="shared" si="13"/>
+        <v>7.5206611570247954</v>
+      </c>
+      <c r="Y31" s="13">
+        <f t="shared" si="13"/>
+        <v>-8.942975206611567E-2</v>
+      </c>
+      <c r="Z31" s="13">
+        <f t="shared" si="13"/>
+        <v>-1.3454545454545467E-2</v>
+      </c>
+      <c r="AA31" s="13">
+        <f t="shared" si="13"/>
+        <v>0.11390909090909092</v>
+      </c>
+      <c r="AB31" s="13">
+        <f t="shared" si="13"/>
+        <v>7.8595041322314065</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <f t="shared" ref="B32:G32" si="14">B31/$D$31</f>
+        <v>0.53858317520556609</v>
+      </c>
+      <c r="C32">
         <f t="shared" si="14"/>
-        <v>9.870129870129869</v>
-      </c>
-      <c r="S31" s="13">
+        <v>0.36527514231499053</v>
+      </c>
+      <c r="D32">
         <f t="shared" si="14"/>
-        <v>21.961038961038959</v>
-      </c>
-      <c r="T31" s="13">
+        <v>1</v>
+      </c>
+      <c r="E32">
         <f t="shared" si="14"/>
-        <v>13.181818181818182</v>
-      </c>
-      <c r="U31" s="13">
+        <v>0.33902593295382671</v>
+      </c>
+      <c r="F32">
         <f t="shared" si="14"/>
-        <v>2.3337662337662383E-3</v>
-      </c>
-      <c r="V31" s="13">
+        <v>1.4705882352941183E-4</v>
+      </c>
+      <c r="G32">
         <f t="shared" si="14"/>
-        <v>4.3454545454545464E-3</v>
-      </c>
-      <c r="W31" s="13">
-        <f t="shared" si="14"/>
-        <v>78.233766233766232</v>
-      </c>
-      <c r="X31" s="13">
-        <f t="shared" si="14"/>
-        <v>7.8181818181818166</v>
-      </c>
-      <c r="Y31" s="13">
-        <f t="shared" si="14"/>
-        <v>-9.2012987012986963E-2</v>
-      </c>
-      <c r="Z31" s="13">
-        <f t="shared" si="14"/>
-        <v>-1.5012987012987004E-2</v>
-      </c>
-      <c r="AA31" s="13">
-        <f t="shared" si="14"/>
-        <v>0.11562337662337657</v>
-      </c>
-      <c r="AB31" s="13">
-        <f t="shared" si="14"/>
-        <v>9.5974025974025992</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B32">
-        <f t="shared" ref="B32:G32" si="15">B31/$D$31</f>
-        <v>0.53858317520556609</v>
-      </c>
-      <c r="C32">
+        <v>1.3678051865907652E-4</v>
+      </c>
+      <c r="H32">
+        <f t="shared" ref="H32:M32" si="15">H31/$H$31</f>
+        <v>1</v>
+      </c>
+      <c r="I32">
         <f t="shared" si="15"/>
-        <v>0.36527514231499053</v>
-      </c>
-      <c r="D32">
+        <v>7.146019658195342E-2</v>
+      </c>
+      <c r="J32">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="E32">
+        <v>-1.6646595235986896E-3</v>
+      </c>
+      <c r="K32">
         <f t="shared" si="15"/>
-        <v>0.33902593295382671</v>
-      </c>
-      <c r="F32">
+        <v>-2.0366598778004082E-4</v>
+      </c>
+      <c r="L32">
         <f t="shared" si="15"/>
-        <v>1.4705882352941183E-4</v>
-      </c>
-      <c r="G32">
+        <v>1.0843885592845123E-3</v>
+      </c>
+      <c r="M32">
         <f t="shared" si="15"/>
-        <v>1.3678051865907652E-4</v>
-      </c>
-      <c r="H32">
-        <f t="shared" ref="H32:M32" si="16">H31/$H$31</f>
-        <v>1</v>
-      </c>
-      <c r="I32">
-        <f t="shared" si="16"/>
-        <v>7.146019658195342E-2</v>
-      </c>
-      <c r="J32">
-        <f t="shared" si="16"/>
-        <v>-1.6646595235986896E-3</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="16"/>
-        <v>-2.0366598778004082E-4</v>
-      </c>
-      <c r="L32">
-        <f t="shared" si="16"/>
-        <v>1.0843885592845123E-3</v>
-      </c>
-      <c r="M32">
-        <f t="shared" si="16"/>
         <v>0.14770211635526434</v>
       </c>
       <c r="P32" s="12" t="s">
         <v>27</v>
       </c>
       <c r="Q32" s="13">
-        <f t="shared" ref="Q32:AB32" si="17">MAX(Q3:Q14)</f>
-        <v>1089.7142857142858</v>
+        <f t="shared" ref="Q32:AB32" si="16">MAX(Q3:Q14)</f>
+        <v>1074.909090909091</v>
       </c>
       <c r="R32" s="13">
-        <f t="shared" si="17"/>
-        <v>334.57142857142856</v>
+        <f t="shared" si="16"/>
+        <v>335.09090909090907</v>
       </c>
       <c r="S32" s="13">
-        <f t="shared" si="17"/>
-        <v>1084.1428571428571</v>
+        <f t="shared" si="16"/>
+        <v>1081.5454545454545</v>
       </c>
       <c r="T32" s="13">
-        <f t="shared" si="17"/>
-        <v>235.2</v>
+        <f t="shared" si="16"/>
+        <v>216.18181818181819</v>
       </c>
       <c r="U32" s="13">
-        <f t="shared" si="17"/>
-        <v>0.34145714285714285</v>
+        <f t="shared" si="16"/>
+        <v>0.34179999999999999</v>
       </c>
       <c r="V32" s="13">
-        <f t="shared" si="17"/>
-        <v>0.4607</v>
+        <f t="shared" si="16"/>
+        <v>0.46048181818181805</v>
       </c>
       <c r="W32" s="13">
-        <f t="shared" si="17"/>
-        <v>1848.1428571428571</v>
+        <f t="shared" si="16"/>
+        <v>1800.4545454545455</v>
       </c>
       <c r="X32" s="13">
-        <f t="shared" si="17"/>
-        <v>139.42857142857142</v>
+        <f t="shared" si="16"/>
+        <v>132.36363636363637</v>
       </c>
       <c r="Y32" s="13">
-        <f t="shared" si="17"/>
-        <v>4.3785714285714281</v>
+        <f t="shared" si="16"/>
+        <v>4.3376363636363635</v>
       </c>
       <c r="Z32" s="13">
-        <f t="shared" si="17"/>
-        <v>1.2785714285714285</v>
+        <f t="shared" si="16"/>
+        <v>1.2714545454545456</v>
       </c>
       <c r="AA32" s="13">
-        <f t="shared" si="17"/>
-        <v>3.9281428571428569</v>
+        <f t="shared" si="16"/>
+        <v>3.8891818181818181</v>
       </c>
       <c r="AB32" s="13">
-        <f t="shared" si="17"/>
-        <v>146.71428571428572</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="16"/>
+        <v>138.45454545454547</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>2021</v>
       </c>
@@ -3646,55 +3694,55 @@
         <v>28</v>
       </c>
       <c r="Q33" s="13">
-        <f t="shared" ref="Q33:AB33" si="18">MIN(Q3:Q14)</f>
-        <v>903.57142857142856</v>
+        <f t="shared" ref="Q33:AB33" si="17">MIN(Q3:Q14)</f>
+        <v>884.81818181818187</v>
       </c>
       <c r="R33" s="13">
-        <f t="shared" si="18"/>
-        <v>226</v>
+        <f t="shared" si="17"/>
+        <v>212.18181818181819</v>
       </c>
       <c r="S33" s="13">
-        <f t="shared" si="18"/>
-        <v>842.57142857142856</v>
+        <f t="shared" si="17"/>
+        <v>818.36363636363637</v>
       </c>
       <c r="T33" s="13">
-        <f t="shared" si="18"/>
-        <v>90.2</v>
+        <f t="shared" si="17"/>
+        <v>75.727272727272734</v>
       </c>
       <c r="U33" s="13">
-        <f t="shared" si="18"/>
-        <v>0.31578571428571423</v>
+        <f t="shared" si="17"/>
+        <v>0.3146272727272727</v>
       </c>
       <c r="V33" s="13">
-        <f t="shared" si="18"/>
-        <v>0.41289999999999999</v>
+        <f t="shared" si="17"/>
+        <v>0.41210000000000002</v>
       </c>
       <c r="W33" s="13">
-        <f t="shared" si="18"/>
-        <v>987.57142857142856</v>
+        <f t="shared" si="17"/>
+        <v>978.63636363636363</v>
       </c>
       <c r="X33" s="13">
-        <f t="shared" si="18"/>
-        <v>53.428571428571431</v>
+        <f t="shared" si="17"/>
+        <v>49.636363636363633</v>
       </c>
       <c r="Y33" s="13">
-        <f t="shared" si="18"/>
-        <v>3.3664285714285715</v>
+        <f t="shared" si="17"/>
+        <v>3.3539090909090912</v>
       </c>
       <c r="Z33" s="13">
-        <f t="shared" si="18"/>
-        <v>1.1134285714285714</v>
+        <f t="shared" si="17"/>
+        <v>1.1234545454545455</v>
       </c>
       <c r="AA33" s="13">
-        <f t="shared" si="18"/>
-        <v>2.6562857142857146</v>
+        <f t="shared" si="17"/>
+        <v>2.636181818181818</v>
       </c>
       <c r="AB33" s="13">
-        <f t="shared" si="18"/>
-        <v>41.142857142857146</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="17"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>29</v>
       </c>
@@ -3738,55 +3786,55 @@
         <v>31</v>
       </c>
       <c r="Q34" s="13">
-        <f t="shared" ref="Q34:AB34" si="19">100*Q19/Q17</f>
-        <v>5.6094162758110553</v>
+        <f t="shared" ref="Q34:AB34" si="18">100*Q19/Q17</f>
+        <v>5.8450766113158856</v>
       </c>
       <c r="R34" s="13">
-        <f t="shared" si="19"/>
-        <v>10.43413202480715</v>
+        <f t="shared" si="18"/>
+        <v>11.325233108265591</v>
       </c>
       <c r="S34" s="13">
-        <f t="shared" si="19"/>
-        <v>6.6797580213416214</v>
+        <f t="shared" si="18"/>
+        <v>7.2385642431921449</v>
       </c>
       <c r="T34" s="13">
-        <f t="shared" si="19"/>
-        <v>26.834974393003584</v>
+        <f t="shared" si="18"/>
+        <v>26.834944548503831</v>
       </c>
       <c r="U34" s="13">
-        <f t="shared" si="19"/>
-        <v>2.3101077292803285</v>
+        <f t="shared" si="18"/>
+        <v>2.2835999048637978</v>
       </c>
       <c r="V34" s="13">
-        <f t="shared" si="19"/>
-        <v>3.0729874870674894</v>
+        <f t="shared" si="18"/>
+        <v>3.0650858299179635</v>
       </c>
       <c r="W34" s="13">
-        <f t="shared" si="19"/>
-        <v>16.177470403839141</v>
+        <f t="shared" si="18"/>
+        <v>16.128290607571344</v>
       </c>
       <c r="X34" s="13">
-        <f t="shared" si="19"/>
-        <v>23.034661019498117</v>
+        <f t="shared" si="18"/>
+        <v>22.557821199984179</v>
       </c>
       <c r="Y34" s="13">
-        <f t="shared" si="19"/>
-        <v>8.0045294093879686</v>
+        <f t="shared" si="18"/>
+        <v>7.2577585789339532</v>
       </c>
       <c r="Z34" s="13">
-        <f t="shared" si="19"/>
-        <v>4.2036132520042369</v>
+        <f t="shared" si="18"/>
+        <v>3.6047721838830782</v>
       </c>
       <c r="AA34" s="13">
-        <f t="shared" si="19"/>
-        <v>10.941292568046361</v>
+        <f t="shared" si="18"/>
+        <v>10.611609884964896</v>
       </c>
       <c r="AB34" s="13">
-        <f t="shared" si="19"/>
-        <v>30.29691423659164</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="18"/>
+        <v>25.581702514045602</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14">
         <v>1</v>
       </c>
@@ -3866,7 +3914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14">
         <v>2</v>
       </c>
@@ -3943,7 +3991,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14">
         <v>3</v>
       </c>
@@ -3988,54 +4036,54 @@
       </c>
       <c r="Q37" s="5">
         <f>Q5</f>
-        <v>1059.8571428571429</v>
+        <v>1049.3636363636363</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" ref="R37:AB37" si="20">R5</f>
-        <v>303.42857142857144</v>
+        <f t="shared" ref="R37:AB37" si="19">R5</f>
+        <v>300</v>
       </c>
       <c r="S37" s="5">
-        <f t="shared" si="20"/>
-        <v>1018.2857142857143</v>
+        <f t="shared" si="19"/>
+        <v>1013.0909090909091</v>
       </c>
       <c r="T37" s="5">
-        <f t="shared" si="20"/>
-        <v>222</v>
+        <f t="shared" si="19"/>
+        <v>194.81818181818181</v>
       </c>
       <c r="U37" s="5">
-        <f t="shared" si="20"/>
-        <v>0.33421428571428569</v>
+        <f t="shared" si="19"/>
+        <v>0.33337272727272732</v>
       </c>
       <c r="V37" s="5">
-        <f t="shared" si="20"/>
-        <v>0.4450142857142857</v>
+        <f t="shared" si="19"/>
+        <v>0.44380909090909082</v>
       </c>
       <c r="W37" s="5">
-        <f t="shared" si="20"/>
-        <v>1657.7142857142858</v>
+        <f t="shared" si="19"/>
+        <v>1646.5454545454545</v>
       </c>
       <c r="X37" s="5">
-        <f t="shared" si="20"/>
-        <v>114.14285714285714</v>
+        <f t="shared" si="19"/>
+        <v>111.18181818181819</v>
       </c>
       <c r="Y37" s="5">
-        <f t="shared" si="20"/>
-        <v>3.5199999999999996</v>
+        <f t="shared" si="19"/>
+        <v>3.5865454545454543</v>
       </c>
       <c r="Z37" s="5">
-        <f t="shared" si="20"/>
-        <v>1.1564285714285716</v>
+        <f t="shared" si="19"/>
+        <v>1.163909090909091</v>
       </c>
       <c r="AA37" s="5">
-        <f t="shared" si="20"/>
-        <v>3.5962857142857141</v>
+        <f t="shared" si="19"/>
+        <v>3.4907272727272725</v>
       </c>
       <c r="AB37" s="5">
-        <f t="shared" si="20"/>
-        <v>113.42857142857143</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28" ht="44.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="19"/>
+        <v>116.18181818181819</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14">
         <v>4</v>
       </c>
@@ -4080,54 +4128,54 @@
       </c>
       <c r="Q38" s="17">
         <f>Q37/13</f>
-        <v>81.527472527472526</v>
+        <v>80.720279720279706</v>
       </c>
       <c r="R38" s="17">
         <f>R37/13</f>
-        <v>23.340659340659343</v>
+        <v>23.076923076923077</v>
       </c>
       <c r="S38" s="17">
         <f>S37/13</f>
-        <v>78.329670329670336</v>
+        <v>77.930069930069934</v>
       </c>
       <c r="T38" s="17">
         <f>T37/13</f>
-        <v>17.076923076923077</v>
+        <v>14.986013986013985</v>
       </c>
       <c r="U38" s="17">
         <f>U37</f>
-        <v>0.33421428571428569</v>
+        <v>0.33337272727272732</v>
       </c>
       <c r="V38" s="17">
         <f>V37</f>
-        <v>0.4450142857142857</v>
+        <v>0.44380909090909082</v>
       </c>
       <c r="W38" s="17">
         <f>W37/9</f>
-        <v>184.1904761904762</v>
+        <v>182.94949494949495</v>
       </c>
       <c r="X38" s="17">
         <f>X37/9</f>
-        <v>12.682539682539682</v>
+        <v>12.353535353535355</v>
       </c>
       <c r="Y38" s="17">
         <f>Y37</f>
-        <v>3.5199999999999996</v>
+        <v>3.5865454545454543</v>
       </c>
       <c r="Z38" s="17">
         <f>Z37</f>
-        <v>1.1564285714285716</v>
+        <v>1.163909090909091</v>
       </c>
       <c r="AA38" s="17">
         <f>AA37</f>
-        <v>3.5962857142857141</v>
+        <v>3.4907272727272725</v>
       </c>
       <c r="AB38" s="17">
         <f>AB37/9</f>
-        <v>12.603174603174603</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12.90909090909091</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" ht="61.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14">
         <v>5</v>
       </c>
@@ -4172,54 +4220,54 @@
       </c>
       <c r="Q39" s="5">
         <f>3*SLOPE(Q4:Q13,$P$4:$P$13)+INTERCEPT(Q4:Q13,$P$4:$P$13)</f>
-        <v>1059.0796536796536</v>
+        <v>1053.3471074380166</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" ref="R39:AB39" si="21">3*SLOPE(R4:R13,$P$4:$P$13)+INTERCEPT(R4:R13,$P$4:$P$13)</f>
-        <v>306.94891774891778</v>
+        <f t="shared" ref="R39:AB39" si="20">3*SLOPE(R4:R13,$P$4:$P$13)+INTERCEPT(R4:R13,$P$4:$P$13)</f>
+        <v>305.38732782369146</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" si="21"/>
-        <v>1021.0199134199136</v>
+        <f t="shared" si="20"/>
+        <v>1016.0429752066117</v>
       </c>
       <c r="T39" s="5">
-        <f t="shared" si="21"/>
-        <v>210.62303030303033</v>
+        <f t="shared" si="20"/>
+        <v>193.48429752066119</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="21"/>
-        <v>0.33531324675324686</v>
+        <f t="shared" si="20"/>
+        <v>0.33418953168044074</v>
       </c>
       <c r="V39" s="5">
-        <f t="shared" si="21"/>
-        <v>0.4458731601731602</v>
+        <f t="shared" si="20"/>
+        <v>0.44459652892561979</v>
       </c>
       <c r="W39" s="5">
-        <f t="shared" si="21"/>
-        <v>1653.3506493506495</v>
+        <f t="shared" si="20"/>
+        <v>1653.1041322314049</v>
       </c>
       <c r="X39" s="5">
-        <f t="shared" si="21"/>
-        <v>117.08051948051948</v>
+        <f t="shared" si="20"/>
+        <v>114.01652892561984</v>
       </c>
       <c r="Y39" s="5">
-        <f t="shared" si="21"/>
-        <v>3.5292995670995664</v>
+        <f t="shared" si="20"/>
+        <v>3.5713614325068876</v>
       </c>
       <c r="Z39" s="5">
-        <f t="shared" si="21"/>
-        <v>1.1561826839826839</v>
+        <f t="shared" si="20"/>
+        <v>1.1672192837465565</v>
       </c>
       <c r="AA39" s="5">
-        <f t="shared" si="21"/>
-        <v>3.6082580086580078</v>
+        <f t="shared" si="20"/>
+        <v>3.5161046831955929</v>
       </c>
       <c r="AB39" s="5">
-        <f t="shared" si="21"/>
-        <v>116.23203463203461</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="20"/>
+        <v>117.78071625344353</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14">
         <v>6</v>
       </c>
@@ -4264,54 +4312,54 @@
       </c>
       <c r="Q40" s="17">
         <f>Q39/13</f>
-        <v>81.467665667665656</v>
+        <v>81.026700572155121</v>
       </c>
       <c r="R40" s="17">
         <f>R39/13</f>
-        <v>23.611455211455215</v>
+        <v>23.491332909514728</v>
       </c>
       <c r="S40" s="17">
         <f>S39/13</f>
-        <v>78.539993339993345</v>
+        <v>78.157151938970131</v>
       </c>
       <c r="T40" s="17">
         <f>T39/13</f>
-        <v>16.201771561771565</v>
+        <v>14.883407501589321</v>
       </c>
       <c r="U40" s="17">
         <f>U39</f>
-        <v>0.33531324675324686</v>
+        <v>0.33418953168044074</v>
       </c>
       <c r="V40" s="17">
         <f>V39</f>
-        <v>0.4458731601731602</v>
+        <v>0.44459652892561979</v>
       </c>
       <c r="W40" s="17">
         <f>W39/9</f>
-        <v>183.70562770562773</v>
+        <v>183.67823691460055</v>
       </c>
       <c r="X40" s="17">
         <f>X39/9</f>
-        <v>13.008946608946609</v>
+        <v>12.668503213957759</v>
       </c>
       <c r="Y40" s="17">
         <f>Y39</f>
-        <v>3.5292995670995664</v>
+        <v>3.5713614325068876</v>
       </c>
       <c r="Z40" s="17">
         <f>Z39</f>
-        <v>1.1561826839826839</v>
+        <v>1.1672192837465565</v>
       </c>
       <c r="AA40" s="17">
         <f>AA39</f>
-        <v>3.6082580086580078</v>
+        <v>3.5161046831955929</v>
       </c>
       <c r="AB40" s="17">
         <f>AB39/9</f>
-        <v>12.914670514670512</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>13.086746250382614</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="14">
         <v>7</v>
       </c>
@@ -4355,55 +4403,55 @@
         <v>36</v>
       </c>
       <c r="Q41">
-        <f t="shared" ref="Q41:AB41" si="22">_xlfn.QUARTILE.INC(Q3:Q14,1)</f>
-        <v>964.78571428571422</v>
+        <f t="shared" ref="Q41:AB41" si="21">_xlfn.QUARTILE.INC(Q3:Q14,1)</f>
+        <v>951.22727272727275</v>
       </c>
       <c r="R41">
-        <f t="shared" si="22"/>
-        <v>259.35714285714289</v>
+        <f t="shared" si="21"/>
+        <v>259.77272727272725</v>
       </c>
       <c r="S41">
-        <f t="shared" si="22"/>
-        <v>926.21428571428578</v>
+        <f t="shared" si="21"/>
+        <v>915.59090909090912</v>
       </c>
       <c r="T41">
-        <f t="shared" si="22"/>
-        <v>134.25</v>
+        <f t="shared" si="21"/>
+        <v>126.88636363636364</v>
       </c>
       <c r="U41">
-        <f t="shared" si="22"/>
-        <v>0.3218428571428571</v>
+        <f t="shared" si="21"/>
+        <v>0.32218181818181818</v>
       </c>
       <c r="V41">
-        <f t="shared" si="22"/>
-        <v>0.42591071428571431</v>
+        <f t="shared" si="21"/>
+        <v>0.42529772727272724</v>
       </c>
       <c r="W41">
-        <f t="shared" si="22"/>
-        <v>1298.3928571428571</v>
+        <f t="shared" si="21"/>
+        <v>1254.7954545454545</v>
       </c>
       <c r="X41">
-        <f t="shared" si="22"/>
-        <v>85.678571428571416</v>
+        <f t="shared" si="21"/>
+        <v>86.61363636363636</v>
       </c>
       <c r="Y41">
-        <f t="shared" si="22"/>
-        <v>3.6049642857142858</v>
+        <f t="shared" si="21"/>
+        <v>3.6460681818181819</v>
       </c>
       <c r="Z41">
-        <f t="shared" si="22"/>
-        <v>1.1686428571428571</v>
+        <f t="shared" si="21"/>
+        <v>1.1793181818181817</v>
       </c>
       <c r="AA41">
-        <f t="shared" si="22"/>
-        <v>3.0314999999999994</v>
+        <f t="shared" si="21"/>
+        <v>2.9982272727272732</v>
       </c>
       <c r="AB41">
-        <f t="shared" si="22"/>
-        <v>74.071428571428569</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="21"/>
+        <v>76.590909090909093</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14">
         <v>8</v>
       </c>
@@ -4447,55 +4495,55 @@
         <v>37</v>
       </c>
       <c r="Q42">
-        <f t="shared" ref="Q42:AB42" si="23">_xlfn.QUARTILE.INC(Q3:Q14,3)</f>
-        <v>1049.0357142857142</v>
+        <f t="shared" ref="Q42:AB42" si="22">_xlfn.QUARTILE.INC(Q3:Q14,3)</f>
+        <v>1040.568181818182</v>
       </c>
       <c r="R42">
-        <f t="shared" si="23"/>
-        <v>300.10714285714289</v>
+        <f t="shared" si="22"/>
+        <v>296.79545454545456</v>
       </c>
       <c r="S42">
-        <f t="shared" si="23"/>
-        <v>1010.1428571428571</v>
+        <f t="shared" si="22"/>
+        <v>1001.9090909090909</v>
       </c>
       <c r="T42">
-        <f t="shared" si="23"/>
-        <v>199.95</v>
+        <f t="shared" si="22"/>
+        <v>183.5</v>
       </c>
       <c r="U42">
-        <f t="shared" si="23"/>
-        <v>0.33363571428571426</v>
+        <f t="shared" si="22"/>
+        <v>0.33205000000000001</v>
       </c>
       <c r="V42">
-        <f t="shared" si="23"/>
-        <v>0.4419392857142857</v>
+        <f t="shared" si="22"/>
+        <v>0.44163409090909084</v>
       </c>
       <c r="W42">
-        <f t="shared" si="23"/>
-        <v>1599.9642857142858</v>
+        <f t="shared" si="22"/>
+        <v>1601.068181818182</v>
       </c>
       <c r="X42">
-        <f t="shared" si="23"/>
-        <v>111.03571428571428</v>
+        <f t="shared" si="22"/>
+        <v>108.93181818181819</v>
       </c>
       <c r="Y42">
-        <f t="shared" si="23"/>
-        <v>4.0825000000000005</v>
+        <f t="shared" si="22"/>
+        <v>4.0251363636363635</v>
       </c>
       <c r="Z42">
-        <f t="shared" si="23"/>
-        <v>1.2564642857142858</v>
+        <f t="shared" si="22"/>
+        <v>1.2472045454545455</v>
       </c>
       <c r="AA42">
-        <f t="shared" si="23"/>
-        <v>3.5381071428571427</v>
+        <f t="shared" si="22"/>
+        <v>3.447159090909091</v>
       </c>
       <c r="AB42">
-        <f t="shared" si="23"/>
-        <v>109.89285714285714</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="22"/>
+        <v>112.02272727272728</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14">
         <v>9</v>
       </c>
@@ -4540,54 +4588,54 @@
       </c>
       <c r="Q43">
         <f>Q42-Q41</f>
-        <v>84.25</v>
+        <v>89.340909090909236</v>
       </c>
       <c r="R43">
-        <f t="shared" ref="R43:AB43" si="24">R42-R41</f>
-        <v>40.75</v>
+        <f t="shared" ref="R43:AB43" si="23">R42-R41</f>
+        <v>37.022727272727309</v>
       </c>
       <c r="S43">
-        <f t="shared" si="24"/>
-        <v>83.928571428571331</v>
+        <f t="shared" si="23"/>
+        <v>86.318181818181756</v>
       </c>
       <c r="T43">
-        <f t="shared" si="24"/>
-        <v>65.699999999999989</v>
+        <f t="shared" si="23"/>
+        <v>56.61363636363636</v>
       </c>
       <c r="U43">
-        <f t="shared" si="24"/>
-        <v>1.179285714285716E-2</v>
+        <f t="shared" si="23"/>
+        <v>9.8681818181818315E-3</v>
       </c>
       <c r="V43">
-        <f t="shared" si="24"/>
-        <v>1.6028571428571392E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.6336363636363593E-2</v>
       </c>
       <c r="W43">
-        <f t="shared" si="24"/>
-        <v>301.57142857142867</v>
+        <f t="shared" si="23"/>
+        <v>346.27272727272748</v>
       </c>
       <c r="X43">
-        <f t="shared" si="24"/>
-        <v>25.357142857142861</v>
+        <f t="shared" si="23"/>
+        <v>22.318181818181827</v>
       </c>
       <c r="Y43">
-        <f t="shared" si="24"/>
-        <v>0.47753571428571462</v>
+        <f t="shared" si="23"/>
+        <v>0.37906818181818158</v>
       </c>
       <c r="Z43">
-        <f t="shared" si="24"/>
-        <v>8.7821428571428717E-2</v>
+        <f t="shared" si="23"/>
+        <v>6.78863636363638E-2</v>
       </c>
       <c r="AA43">
-        <f t="shared" si="24"/>
-        <v>0.50660714285714326</v>
+        <f t="shared" si="23"/>
+        <v>0.44893181818181782</v>
       </c>
       <c r="AB43">
-        <f t="shared" si="24"/>
-        <v>35.821428571428569</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="23"/>
+        <v>35.431818181818187</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14">
         <v>10</v>
       </c>
@@ -4632,54 +4680,54 @@
       </c>
       <c r="Q44">
         <f>Q41-Q43</f>
-        <v>880.53571428571422</v>
+        <v>861.88636363636351</v>
       </c>
       <c r="R44">
-        <f t="shared" ref="R44:AB44" si="25">R41-R43</f>
-        <v>218.60714285714289</v>
+        <f t="shared" ref="R44:AB44" si="24">R41-R43</f>
+        <v>222.74999999999994</v>
       </c>
       <c r="S44">
-        <f t="shared" si="25"/>
-        <v>842.28571428571445</v>
+        <f t="shared" si="24"/>
+        <v>829.27272727272737</v>
       </c>
       <c r="T44">
-        <f t="shared" si="25"/>
-        <v>68.550000000000011</v>
+        <f t="shared" si="24"/>
+        <v>70.27272727272728</v>
       </c>
       <c r="U44">
-        <f t="shared" si="25"/>
-        <v>0.31004999999999994</v>
+        <f t="shared" si="24"/>
+        <v>0.31231363636363635</v>
       </c>
       <c r="V44">
-        <f t="shared" si="25"/>
-        <v>0.40988214285714292</v>
+        <f t="shared" si="24"/>
+        <v>0.40896136363636365</v>
       </c>
       <c r="W44">
-        <f t="shared" si="25"/>
-        <v>996.82142857142844</v>
+        <f t="shared" si="24"/>
+        <v>908.52272727272702</v>
       </c>
       <c r="X44">
-        <f t="shared" si="25"/>
-        <v>60.321428571428555</v>
+        <f t="shared" si="24"/>
+        <v>64.295454545454533</v>
       </c>
       <c r="Y44">
-        <f t="shared" si="25"/>
-        <v>3.1274285714285712</v>
+        <f t="shared" si="24"/>
+        <v>3.2670000000000003</v>
       </c>
       <c r="Z44">
-        <f t="shared" si="25"/>
-        <v>1.0808214285714284</v>
+        <f t="shared" si="24"/>
+        <v>1.1114318181818179</v>
       </c>
       <c r="AA44">
-        <f t="shared" si="25"/>
-        <v>2.5248928571428562</v>
+        <f t="shared" si="24"/>
+        <v>2.5492954545454554</v>
       </c>
       <c r="AB44">
-        <f t="shared" si="25"/>
-        <v>38.25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="24"/>
+        <v>41.159090909090907</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14">
         <v>11</v>
       </c>
@@ -4724,54 +4772,54 @@
       </c>
       <c r="Q45">
         <f>Q42+Q43</f>
-        <v>1133.2857142857142</v>
+        <v>1129.9090909090912</v>
       </c>
       <c r="R45">
-        <f t="shared" ref="R45:AB45" si="26">R42+R43</f>
-        <v>340.85714285714289</v>
+        <f t="shared" ref="R45:AB45" si="25">R42+R43</f>
+        <v>333.81818181818187</v>
       </c>
       <c r="S45">
-        <f t="shared" si="26"/>
-        <v>1094.0714285714284</v>
+        <f t="shared" si="25"/>
+        <v>1088.2272727272725</v>
       </c>
       <c r="T45">
-        <f t="shared" si="26"/>
-        <v>265.64999999999998</v>
+        <f t="shared" si="25"/>
+        <v>240.11363636363637</v>
       </c>
       <c r="U45">
-        <f t="shared" si="26"/>
-        <v>0.34542857142857142</v>
+        <f t="shared" si="25"/>
+        <v>0.34191818181818184</v>
       </c>
       <c r="V45">
-        <f t="shared" si="26"/>
-        <v>0.45796785714285709</v>
+        <f t="shared" si="25"/>
+        <v>0.45797045454545443</v>
       </c>
       <c r="W45">
-        <f t="shared" si="26"/>
-        <v>1901.5357142857144</v>
+        <f t="shared" si="25"/>
+        <v>1947.3409090909095</v>
       </c>
       <c r="X45">
-        <f t="shared" si="26"/>
-        <v>136.39285714285714</v>
+        <f t="shared" si="25"/>
+        <v>131.25</v>
       </c>
       <c r="Y45">
-        <f t="shared" si="26"/>
-        <v>4.5600357142857151</v>
+        <f t="shared" si="25"/>
+        <v>4.4042045454545455</v>
       </c>
       <c r="Z45">
-        <f t="shared" si="26"/>
-        <v>1.3442857142857145</v>
+        <f t="shared" si="25"/>
+        <v>1.3150909090909093</v>
       </c>
       <c r="AA45">
-        <f t="shared" si="26"/>
-        <v>4.0447142857142859</v>
+        <f t="shared" si="25"/>
+        <v>3.8960909090909088</v>
       </c>
       <c r="AB45">
-        <f t="shared" si="26"/>
-        <v>145.71428571428572</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="25"/>
+        <v>147.45454545454547</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14">
         <v>12</v>
       </c>
@@ -4812,108 +4860,108 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B47">
-        <f t="shared" ref="B47:G47" si="27">-1*SLOPE(B36:B45,$A$36:$A$45)</f>
+        <f t="shared" ref="B47:G47" si="26">-1*SLOPE(B36:B45,$A$36:$A$45)</f>
         <v>18.145454545454545</v>
       </c>
       <c r="C47">
+        <f t="shared" si="26"/>
+        <v>5.872727272727273</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="26"/>
+        <v>15.927272727272728</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="26"/>
+        <v>8.2666666666666675</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="26"/>
+        <v>1.7521212121212083E-3</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="26"/>
+        <v>3.2678787878787901E-3</v>
+      </c>
+      <c r="H47">
+        <f t="shared" ref="H47:M47" si="27">-1*SLOPE(H36:H45,$A$20:$A$29)</f>
+        <v>53.472727272727276</v>
+      </c>
+      <c r="I47">
         <f t="shared" si="27"/>
-        <v>5.872727272727273</v>
-      </c>
-      <c r="D47">
+        <v>5.0666666666666664</v>
+      </c>
+      <c r="J47">
         <f t="shared" si="27"/>
-        <v>15.927272727272728</v>
-      </c>
-      <c r="E47">
+        <v>-7.4799999999999978E-2</v>
+      </c>
+      <c r="K47">
         <f t="shared" si="27"/>
-        <v>8.2666666666666675</v>
-      </c>
-      <c r="F47">
+        <v>-1.0751515151515166E-2</v>
+      </c>
+      <c r="L47">
         <f t="shared" si="27"/>
-        <v>1.7521212121212083E-3</v>
-      </c>
-      <c r="G47">
+        <v>0.10242424242424242</v>
+      </c>
+      <c r="M47">
         <f t="shared" si="27"/>
-        <v>3.2678787878787901E-3</v>
-      </c>
-      <c r="H47">
-        <f t="shared" ref="H47:M47" si="28">-1*SLOPE(H36:H45,$A$20:$A$29)</f>
-        <v>53.472727272727276</v>
-      </c>
-      <c r="I47">
+        <v>10.036363636363637</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <f t="shared" ref="B48:G48" si="28">B47/$D$47</f>
+        <v>1.139269406392694</v>
+      </c>
+      <c r="C48">
         <f t="shared" si="28"/>
-        <v>5.0666666666666664</v>
-      </c>
-      <c r="J47">
+        <v>0.36872146118721461</v>
+      </c>
+      <c r="D48">
         <f t="shared" si="28"/>
-        <v>-7.4799999999999978E-2</v>
-      </c>
-      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="E48">
         <f t="shared" si="28"/>
-        <v>-1.0751515151515166E-2</v>
-      </c>
-      <c r="L47">
+        <v>0.51902587519025878</v>
+      </c>
+      <c r="F48">
         <f t="shared" si="28"/>
-        <v>0.10242424242424242</v>
-      </c>
-      <c r="M47">
+        <v>1.1000761035007587E-4</v>
+      </c>
+      <c r="G48">
         <f t="shared" si="28"/>
-        <v>10.036363636363637</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B48">
-        <f t="shared" ref="B48:G48" si="29">B47/$D$47</f>
-        <v>1.139269406392694</v>
-      </c>
-      <c r="C48">
+        <v>2.0517503805175051E-4</v>
+      </c>
+      <c r="H48">
+        <f t="shared" ref="H48:M48" si="29">H47/$H$47</f>
+        <v>1</v>
+      </c>
+      <c r="I48">
         <f t="shared" si="29"/>
-        <v>0.36872146118721461</v>
-      </c>
-      <c r="D48">
+        <v>9.4752351807775123E-2</v>
+      </c>
+      <c r="J48">
         <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-      <c r="E48">
+        <v>-1.3988439306358376E-3</v>
+      </c>
+      <c r="K48">
         <f t="shared" si="29"/>
-        <v>0.51902587519025878</v>
-      </c>
-      <c r="F48">
+        <v>-2.0106539725716903E-4</v>
+      </c>
+      <c r="L48">
         <f t="shared" si="29"/>
-        <v>1.1000761035007587E-4</v>
-      </c>
-      <c r="G48">
+        <v>1.9154482602289468E-3</v>
+      </c>
+      <c r="M48">
         <f t="shared" si="29"/>
-        <v>2.0517503805175051E-4</v>
-      </c>
-      <c r="H48">
-        <f t="shared" ref="H48:M48" si="30">H47/$H$47</f>
-        <v>1</v>
-      </c>
-      <c r="I48">
-        <f t="shared" si="30"/>
-        <v>9.4752351807775123E-2</v>
-      </c>
-      <c r="J48">
-        <f t="shared" si="30"/>
-        <v>-1.3988439306358376E-3</v>
-      </c>
-      <c r="K48">
-        <f t="shared" si="30"/>
-        <v>-2.0106539725716903E-4</v>
-      </c>
-      <c r="L48">
-        <f t="shared" si="30"/>
-        <v>1.9154482602289468E-3</v>
-      </c>
-      <c r="M48">
-        <f t="shared" si="30"/>
         <v>0.18769126147568854</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="51" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>2024</v>
       </c>
@@ -4934,7 +4982,7 @@
       <c r="L51" s="24"/>
       <c r="M51" s="24"/>
     </row>
-    <row r="52" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="20" t="s">
         <v>2</v>
       </c>
@@ -4972,7 +5020,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="21">
         <v>981</v>
       </c>
@@ -5010,7 +5058,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="22">
         <v>1084</v>
       </c>
@@ -5048,7 +5096,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="21">
         <v>969</v>
       </c>
@@ -5086,7 +5134,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="21">
         <v>1015</v>
       </c>
@@ -5124,7 +5172,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="21">
         <v>1049</v>
       </c>
@@ -5162,7 +5210,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="21">
         <v>1065</v>
       </c>
@@ -5200,7 +5248,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="21">
         <v>930</v>
       </c>
@@ -5238,7 +5286,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="21">
         <v>1070</v>
       </c>
@@ -5276,7 +5324,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="21">
         <v>976</v>
       </c>
@@ -5314,7 +5362,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="21">
         <v>908</v>
       </c>
@@ -5352,7 +5400,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="21">
         <v>919</v>
       </c>
@@ -5390,7 +5438,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="23">
         <v>907</v>
       </c>
@@ -5428,7 +5476,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2024</v>
       </c>
@@ -5469,7 +5517,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B66" cm="1">
         <f t="array" ref="B66:B77">_xlfn._xlws.SORT(B53:B64,,-1)</f>
         <v>1084</v>
@@ -5519,7 +5567,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>1070</v>
       </c>
@@ -5557,7 +5605,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>1065</v>
       </c>
@@ -5595,7 +5643,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B69">
         <v>1049</v>
       </c>
@@ -5633,7 +5681,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>1015</v>
       </c>
@@ -5671,7 +5719,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>981</v>
       </c>
@@ -5709,7 +5757,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>976</v>
       </c>
@@ -5747,7 +5795,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>969</v>
       </c>
@@ -5785,7 +5833,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>930</v>
       </c>
@@ -5823,7 +5871,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B75">
         <v>919</v>
       </c>
@@ -5861,7 +5909,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B76">
         <v>908</v>
       </c>
@@ -5899,7 +5947,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B77">
         <v>907</v>
       </c>
@@ -5937,10 +5985,1037 @@
         <v>60</v>
       </c>
     </row>
+    <row r="79" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>2025</v>
+      </c>
+      <c r="B80" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C80" s="29"/>
+      <c r="D80" s="29"/>
+      <c r="E80" s="29"/>
+      <c r="F80" s="29"/>
+      <c r="G80" s="29"/>
+      <c r="H80" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" s="29"/>
+      <c r="J80" s="29"/>
+      <c r="K80" s="29"/>
+      <c r="L80" s="29"/>
+      <c r="M80" s="29"/>
+    </row>
+    <row r="81" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G81" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H81" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J81" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="K81" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="L81" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M81" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="26">
+        <v>1010</v>
+      </c>
+      <c r="C82" s="26">
+        <v>290</v>
+      </c>
+      <c r="D82" s="26">
+        <v>1004</v>
+      </c>
+      <c r="E82" s="26">
+        <v>217</v>
+      </c>
+      <c r="F82" s="26">
+        <v>0.31259999999999999</v>
+      </c>
+      <c r="G82" s="26">
+        <v>0.432</v>
+      </c>
+      <c r="H82" s="26">
+        <v>1627</v>
+      </c>
+      <c r="I82" s="26">
+        <v>105</v>
+      </c>
+      <c r="J82" s="26">
+        <v>3.7679999999999998</v>
+      </c>
+      <c r="K82" s="26">
+        <v>1.222</v>
+      </c>
+      <c r="L82" s="26">
+        <v>2.8439999999999999</v>
+      </c>
+      <c r="M82" s="26">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="26">
+        <v>1045</v>
+      </c>
+      <c r="C83" s="26">
+        <v>264</v>
+      </c>
+      <c r="D83" s="26">
+        <v>949</v>
+      </c>
+      <c r="E83" s="26">
+        <v>181</v>
+      </c>
+      <c r="F83" s="26">
+        <v>0.33779999999999999</v>
+      </c>
+      <c r="G83" s="26">
+        <v>0.4325</v>
+      </c>
+      <c r="H83" s="26">
+        <v>1534</v>
+      </c>
+      <c r="I83" s="26">
+        <v>98</v>
+      </c>
+      <c r="J83" s="26">
+        <v>3.7229999999999999</v>
+      </c>
+      <c r="K83" s="26">
+        <v>1.177</v>
+      </c>
+      <c r="L83" s="26">
+        <v>3.306</v>
+      </c>
+      <c r="M83" s="26">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="26">
+        <v>961</v>
+      </c>
+      <c r="C84" s="26">
+        <v>261</v>
+      </c>
+      <c r="D84" s="26">
+        <v>908</v>
+      </c>
+      <c r="E84" s="26">
+        <v>225</v>
+      </c>
+      <c r="F84" s="26">
+        <v>0.32529999999999998</v>
+      </c>
+      <c r="G84" s="26">
+        <v>0.42009999999999997</v>
+      </c>
+      <c r="H84" s="26">
+        <v>1424</v>
+      </c>
+      <c r="I84" s="26">
+        <v>97</v>
+      </c>
+      <c r="J84" s="26">
+        <v>4.141</v>
+      </c>
+      <c r="K84" s="26">
+        <v>1.2450000000000001</v>
+      </c>
+      <c r="L84" s="26">
+        <v>3.1429999999999998</v>
+      </c>
+      <c r="M84" s="26">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="26">
+        <v>1024</v>
+      </c>
+      <c r="C85" s="26">
+        <v>294</v>
+      </c>
+      <c r="D85" s="26">
+        <v>979</v>
+      </c>
+      <c r="E85" s="26">
+        <v>157</v>
+      </c>
+      <c r="F85" s="26">
+        <v>0.34239999999999998</v>
+      </c>
+      <c r="G85" s="26">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="H85" s="26">
+        <v>1717</v>
+      </c>
+      <c r="I85" s="26">
+        <v>111</v>
+      </c>
+      <c r="J85" s="26">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="K85" s="26">
+        <v>1.2190000000000001</v>
+      </c>
+      <c r="L85" s="26">
+        <v>2.7559999999999998</v>
+      </c>
+      <c r="M85" s="26">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="26">
+        <v>1049</v>
+      </c>
+      <c r="C86" s="26">
+        <v>279</v>
+      </c>
+      <c r="D86" s="26">
+        <v>982</v>
+      </c>
+      <c r="E86" s="26">
+        <v>167</v>
+      </c>
+      <c r="F86" s="26">
+        <v>0.32379999999999998</v>
+      </c>
+      <c r="G86" s="26">
+        <v>0.42559999999999998</v>
+      </c>
+      <c r="H86" s="26">
+        <v>1453</v>
+      </c>
+      <c r="I86" s="26">
+        <v>92</v>
+      </c>
+      <c r="J86" s="26">
+        <v>3.6480000000000001</v>
+      </c>
+      <c r="K86" s="26">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="L86" s="26">
+        <v>2.996</v>
+      </c>
+      <c r="M86" s="26">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="27">
+        <v>1031</v>
+      </c>
+      <c r="C87" s="27">
+        <v>336</v>
+      </c>
+      <c r="D87" s="27">
+        <v>1077</v>
+      </c>
+      <c r="E87" s="27">
+        <v>68</v>
+      </c>
+      <c r="F87" s="27">
+        <v>0.32269999999999999</v>
+      </c>
+      <c r="G87" s="27">
+        <v>0.44169999999999998</v>
+      </c>
+      <c r="H87" s="27">
+        <v>1679</v>
+      </c>
+      <c r="I87" s="27">
+        <v>106</v>
+      </c>
+      <c r="J87" s="27">
+        <v>3.73</v>
+      </c>
+      <c r="K87" s="27">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="L87" s="27">
+        <v>3.476</v>
+      </c>
+      <c r="M87" s="27">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B88" s="26">
+        <v>1008</v>
+      </c>
+      <c r="C88" s="26">
+        <v>290</v>
+      </c>
+      <c r="D88" s="26">
+        <v>944</v>
+      </c>
+      <c r="E88" s="26">
+        <v>121</v>
+      </c>
+      <c r="F88" s="26">
+        <v>0.3266</v>
+      </c>
+      <c r="G88" s="26">
+        <v>0.44090000000000001</v>
+      </c>
+      <c r="H88" s="26">
+        <v>1504</v>
+      </c>
+      <c r="I88" s="26">
+        <v>94</v>
+      </c>
+      <c r="J88" s="26">
+        <v>4.266</v>
+      </c>
+      <c r="K88" s="26">
+        <v>1.2589999999999999</v>
+      </c>
+      <c r="L88" s="26">
+        <v>2.972</v>
+      </c>
+      <c r="M88" s="26">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="26">
+        <v>917</v>
+      </c>
+      <c r="C89" s="26">
+        <v>263</v>
+      </c>
+      <c r="D89" s="26">
+        <v>899</v>
+      </c>
+      <c r="E89" s="26">
+        <v>143</v>
+      </c>
+      <c r="F89" s="26">
+        <v>0.32050000000000001</v>
+      </c>
+      <c r="G89" s="26">
+        <v>0.43090000000000001</v>
+      </c>
+      <c r="H89" s="26">
+        <v>1171</v>
+      </c>
+      <c r="I89" s="26">
+        <v>80</v>
+      </c>
+      <c r="J89" s="26">
+        <v>3.867</v>
+      </c>
+      <c r="K89" s="26">
+        <v>1.2130000000000001</v>
+      </c>
+      <c r="L89" s="26">
+        <v>3.165</v>
+      </c>
+      <c r="M89" s="26">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="26">
+        <v>1016</v>
+      </c>
+      <c r="C90" s="26">
+        <v>329</v>
+      </c>
+      <c r="D90" s="26">
+        <v>1029</v>
+      </c>
+      <c r="E90" s="26">
+        <v>193</v>
+      </c>
+      <c r="F90" s="26">
+        <v>0.33189999999999997</v>
+      </c>
+      <c r="G90" s="26">
+        <v>0.46010000000000001</v>
+      </c>
+      <c r="H90" s="26">
+        <v>1148</v>
+      </c>
+      <c r="I90" s="26">
+        <v>63</v>
+      </c>
+      <c r="J90" s="26">
+        <v>3.7029999999999998</v>
+      </c>
+      <c r="K90" s="26">
+        <v>1.228</v>
+      </c>
+      <c r="L90" s="26">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="M90" s="26">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="26">
+        <v>931</v>
+      </c>
+      <c r="C91" s="26">
+        <v>257</v>
+      </c>
+      <c r="D91" s="26">
+        <v>856</v>
+      </c>
+      <c r="E91" s="26">
+        <v>190</v>
+      </c>
+      <c r="F91" s="26">
+        <v>0.32279999999999998</v>
+      </c>
+      <c r="G91" s="26">
+        <v>0.41070000000000001</v>
+      </c>
+      <c r="H91" s="26">
+        <v>1181</v>
+      </c>
+      <c r="I91" s="26">
+        <v>91</v>
+      </c>
+      <c r="J91" s="26">
+        <v>4.0979999999999999</v>
+      </c>
+      <c r="K91" s="26">
+        <v>1.24</v>
+      </c>
+      <c r="L91" s="26">
+        <v>2.601</v>
+      </c>
+      <c r="M91" s="26">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="26">
+        <v>889</v>
+      </c>
+      <c r="C92" s="26">
+        <v>259</v>
+      </c>
+      <c r="D92" s="26">
+        <v>891</v>
+      </c>
+      <c r="E92" s="26">
+        <v>102</v>
+      </c>
+      <c r="F92" s="26">
+        <v>0.32729999999999998</v>
+      </c>
+      <c r="G92" s="26">
+        <v>0.43070000000000003</v>
+      </c>
+      <c r="H92" s="26">
+        <v>1595</v>
+      </c>
+      <c r="I92" s="26">
+        <v>120</v>
+      </c>
+      <c r="J92" s="26">
+        <v>3.3319999999999999</v>
+      </c>
+      <c r="K92" s="26">
+        <v>1.141</v>
+      </c>
+      <c r="L92" s="26">
+        <v>3.282</v>
+      </c>
+      <c r="M92" s="26">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="28">
+        <v>852</v>
+      </c>
+      <c r="C93" s="28">
+        <v>188</v>
+      </c>
+      <c r="D93" s="28">
+        <v>776</v>
+      </c>
+      <c r="E93" s="28">
+        <v>161</v>
+      </c>
+      <c r="F93" s="28">
+        <v>0.32840000000000003</v>
+      </c>
+      <c r="G93" s="28">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="H93" s="28">
+        <v>963</v>
+      </c>
+      <c r="I93" s="28">
+        <v>43</v>
+      </c>
+      <c r="J93" s="28">
+        <v>3.7429999999999999</v>
+      </c>
+      <c r="K93" s="28">
+        <v>1.175</v>
+      </c>
+      <c r="L93" s="28">
+        <v>3.8210000000000002</v>
+      </c>
+      <c r="M93" s="28">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>2025</v>
+      </c>
+      <c r="B94" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="H94" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J94" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="K94" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="L94" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M94" s="25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B95" cm="1">
+        <f t="array" ref="B95:B106">_xlfn._xlws.SORT(B82:B93,,-1)</f>
+        <v>1049</v>
+      </c>
+      <c r="C95" cm="1">
+        <f t="array" ref="C95:C106">_xlfn._xlws.SORT(C82:C93,,-1)</f>
+        <v>336</v>
+      </c>
+      <c r="D95" cm="1">
+        <f t="array" ref="D95:D106">_xlfn._xlws.SORT(D82:D93,,-1)</f>
+        <v>1077</v>
+      </c>
+      <c r="E95" cm="1">
+        <f t="array" ref="E95:E106">_xlfn._xlws.SORT(E82:E93,,-1)</f>
+        <v>225</v>
+      </c>
+      <c r="F95" cm="1">
+        <f t="array" ref="F95:F106">_xlfn._xlws.SORT(F82:F93,,-1)</f>
+        <v>0.34239999999999998</v>
+      </c>
+      <c r="G95" cm="1">
+        <f t="array" ref="G95:G106">_xlfn._xlws.SORT(G82:G93,,-1)</f>
+        <v>0.46010000000000001</v>
+      </c>
+      <c r="H95" cm="1">
+        <f t="array" ref="H95:H106">_xlfn._xlws.SORT(H82:H93,,-1)</f>
+        <v>1717</v>
+      </c>
+      <c r="I95" cm="1">
+        <f t="array" ref="I95:I106">_xlfn._xlws.SORT(I82:I93,,-1)</f>
+        <v>120</v>
+      </c>
+      <c r="J95" cm="1">
+        <f t="array" ref="J95:J106">_xlfn._xlws.SORT(J82:J93,,1)</f>
+        <v>3.3319999999999999</v>
+      </c>
+      <c r="K95" cm="1">
+        <f t="array" ref="K95:K106">_xlfn._xlws.SORT(K82:K93,,1)</f>
+        <v>1.141</v>
+      </c>
+      <c r="L95" cm="1">
+        <f t="array" ref="L95:L106">_xlfn._xlws.SORT(L82:L93,,-1)</f>
+        <v>3.8210000000000002</v>
+      </c>
+      <c r="M95" cm="1">
+        <f t="array" ref="M95:M106">_xlfn._xlws.SORT(M82:M93,,-1)</f>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B96">
+        <v>1045</v>
+      </c>
+      <c r="C96">
+        <v>329</v>
+      </c>
+      <c r="D96">
+        <v>1029</v>
+      </c>
+      <c r="E96">
+        <v>217</v>
+      </c>
+      <c r="F96">
+        <v>0.33779999999999999</v>
+      </c>
+      <c r="G96">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="H96">
+        <v>1679</v>
+      </c>
+      <c r="I96">
+        <v>111</v>
+      </c>
+      <c r="J96">
+        <v>3.6480000000000001</v>
+      </c>
+      <c r="K96">
+        <v>1.175</v>
+      </c>
+      <c r="L96">
+        <v>3.476</v>
+      </c>
+      <c r="M96">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B97">
+        <v>1031</v>
+      </c>
+      <c r="C97">
+        <v>294</v>
+      </c>
+      <c r="D97">
+        <v>1004</v>
+      </c>
+      <c r="E97">
+        <v>193</v>
+      </c>
+      <c r="F97">
+        <v>0.33189999999999997</v>
+      </c>
+      <c r="G97">
+        <v>0.44169999999999998</v>
+      </c>
+      <c r="H97">
+        <v>1627</v>
+      </c>
+      <c r="I97">
+        <v>106</v>
+      </c>
+      <c r="J97">
+        <v>3.7029999999999998</v>
+      </c>
+      <c r="K97">
+        <v>1.177</v>
+      </c>
+      <c r="L97">
+        <v>3.306</v>
+      </c>
+      <c r="M97">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B98">
+        <v>1024</v>
+      </c>
+      <c r="C98">
+        <v>290</v>
+      </c>
+      <c r="D98">
+        <v>982</v>
+      </c>
+      <c r="E98">
+        <v>190</v>
+      </c>
+      <c r="F98">
+        <v>0.32840000000000003</v>
+      </c>
+      <c r="G98">
+        <v>0.44090000000000001</v>
+      </c>
+      <c r="H98">
+        <v>1595</v>
+      </c>
+      <c r="I98">
+        <v>105</v>
+      </c>
+      <c r="J98">
+        <v>3.7229999999999999</v>
+      </c>
+      <c r="K98">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="L98">
+        <v>3.282</v>
+      </c>
+      <c r="M98">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B99">
+        <v>1016</v>
+      </c>
+      <c r="C99">
+        <v>290</v>
+      </c>
+      <c r="D99">
+        <v>979</v>
+      </c>
+      <c r="E99">
+        <v>181</v>
+      </c>
+      <c r="F99">
+        <v>0.32729999999999998</v>
+      </c>
+      <c r="G99">
+        <v>0.4325</v>
+      </c>
+      <c r="H99">
+        <v>1534</v>
+      </c>
+      <c r="I99">
+        <v>98</v>
+      </c>
+      <c r="J99">
+        <v>3.73</v>
+      </c>
+      <c r="K99">
+        <v>1.2050000000000001</v>
+      </c>
+      <c r="L99">
+        <v>3.165</v>
+      </c>
+      <c r="M99">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="100" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B100">
+        <v>1010</v>
+      </c>
+      <c r="C100">
+        <v>279</v>
+      </c>
+      <c r="D100">
+        <v>949</v>
+      </c>
+      <c r="E100">
+        <v>167</v>
+      </c>
+      <c r="F100">
+        <v>0.3266</v>
+      </c>
+      <c r="G100">
+        <v>0.432</v>
+      </c>
+      <c r="H100">
+        <v>1504</v>
+      </c>
+      <c r="I100">
+        <v>97</v>
+      </c>
+      <c r="J100">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="K100">
+        <v>1.2130000000000001</v>
+      </c>
+      <c r="L100">
+        <v>3.1429999999999998</v>
+      </c>
+      <c r="M100">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="101" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B101">
+        <v>1008</v>
+      </c>
+      <c r="C101">
+        <v>264</v>
+      </c>
+      <c r="D101">
+        <v>944</v>
+      </c>
+      <c r="E101">
+        <v>161</v>
+      </c>
+      <c r="F101">
+        <v>0.32529999999999998</v>
+      </c>
+      <c r="G101">
+        <v>0.43090000000000001</v>
+      </c>
+      <c r="H101">
+        <v>1453</v>
+      </c>
+      <c r="I101">
+        <v>94</v>
+      </c>
+      <c r="J101">
+        <v>3.7429999999999999</v>
+      </c>
+      <c r="K101">
+        <v>1.2190000000000001</v>
+      </c>
+      <c r="L101">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="M101">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B102">
+        <v>961</v>
+      </c>
+      <c r="C102">
+        <v>263</v>
+      </c>
+      <c r="D102">
+        <v>908</v>
+      </c>
+      <c r="E102">
+        <v>157</v>
+      </c>
+      <c r="F102">
+        <v>0.32379999999999998</v>
+      </c>
+      <c r="G102">
+        <v>0.43070000000000003</v>
+      </c>
+      <c r="H102">
+        <v>1424</v>
+      </c>
+      <c r="I102">
+        <v>92</v>
+      </c>
+      <c r="J102">
+        <v>3.7679999999999998</v>
+      </c>
+      <c r="K102">
+        <v>1.222</v>
+      </c>
+      <c r="L102">
+        <v>2.996</v>
+      </c>
+      <c r="M102">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="103" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B103">
+        <v>931</v>
+      </c>
+      <c r="C103">
+        <v>261</v>
+      </c>
+      <c r="D103">
+        <v>899</v>
+      </c>
+      <c r="E103">
+        <v>143</v>
+      </c>
+      <c r="F103">
+        <v>0.32279999999999998</v>
+      </c>
+      <c r="G103">
+        <v>0.42559999999999998</v>
+      </c>
+      <c r="H103">
+        <v>1181</v>
+      </c>
+      <c r="I103">
+        <v>91</v>
+      </c>
+      <c r="J103">
+        <v>3.867</v>
+      </c>
+      <c r="K103">
+        <v>1.228</v>
+      </c>
+      <c r="L103">
+        <v>2.972</v>
+      </c>
+      <c r="M103">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="104" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B104">
+        <v>917</v>
+      </c>
+      <c r="C104">
+        <v>259</v>
+      </c>
+      <c r="D104">
+        <v>891</v>
+      </c>
+      <c r="E104">
+        <v>121</v>
+      </c>
+      <c r="F104">
+        <v>0.32269999999999999</v>
+      </c>
+      <c r="G104">
+        <v>0.42009999999999997</v>
+      </c>
+      <c r="H104">
+        <v>1171</v>
+      </c>
+      <c r="I104">
+        <v>80</v>
+      </c>
+      <c r="J104">
+        <v>4.0979999999999999</v>
+      </c>
+      <c r="K104">
+        <v>1.24</v>
+      </c>
+      <c r="L104">
+        <v>2.8439999999999999</v>
+      </c>
+      <c r="M104">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="105" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B105">
+        <v>889</v>
+      </c>
+      <c r="C105">
+        <v>257</v>
+      </c>
+      <c r="D105">
+        <v>856</v>
+      </c>
+      <c r="E105">
+        <v>102</v>
+      </c>
+      <c r="F105">
+        <v>0.32050000000000001</v>
+      </c>
+      <c r="G105">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="H105">
+        <v>1148</v>
+      </c>
+      <c r="I105">
+        <v>63</v>
+      </c>
+      <c r="J105">
+        <v>4.141</v>
+      </c>
+      <c r="K105">
+        <v>1.2450000000000001</v>
+      </c>
+      <c r="L105">
+        <v>2.7559999999999998</v>
+      </c>
+      <c r="M105">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="106" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B106">
+        <v>852</v>
+      </c>
+      <c r="C106">
+        <v>188</v>
+      </c>
+      <c r="D106">
+        <v>776</v>
+      </c>
+      <c r="E106">
+        <v>68</v>
+      </c>
+      <c r="F106">
+        <v>0.31259999999999999</v>
+      </c>
+      <c r="G106">
+        <v>0.41070000000000001</v>
+      </c>
+      <c r="H106">
+        <v>963</v>
+      </c>
+      <c r="I106">
+        <v>43</v>
+      </c>
+      <c r="J106">
+        <v>4.266</v>
+      </c>
+      <c r="K106">
+        <v>1.2589999999999999</v>
+      </c>
+      <c r="L106">
+        <v>2.601</v>
+      </c>
+      <c r="M106">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="H51:M51"/>
+    <mergeCell ref="B80:G80"/>
+    <mergeCell ref="H80:M80"/>
   </mergeCells>
   <conditionalFormatting sqref="Q3:AB14">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
@@ -5958,162 +7033,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9734E317-61B8-40AC-9651-51DC5AB8F31B}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1">
         <f>'Historical Data'!$Q26</f>
-        <v>70.609523809523807</v>
+        <v>69.793006993007012</v>
       </c>
       <c r="C1">
         <f>'Historical Data'!$Q27</f>
-        <v>15.683982683982686</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16.226446280991738</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
         <f>'Historical Data'!$R26</f>
-        <v>18.566300366300368</v>
+        <v>18.550582750582752</v>
       </c>
       <c r="C2">
         <f>'Historical Data'!$R27</f>
-        <v>7.2874458874458883</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>7.1366391184572988</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
         <f>'Historical Data'!$S26</f>
-        <v>67.730402930402946</v>
+        <v>66.730069930069945</v>
       </c>
       <c r="C3">
         <f>'Historical Data'!$S27</f>
-        <v>15.613852813852809</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16.505785123966938</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
         <f>'Historical Data'!$T26</f>
-        <v>7.509743589743592</v>
+        <v>7.1776223776223782</v>
       </c>
       <c r="C4">
         <f>'Historical Data'!$T27</f>
-        <v>12.555151515151515</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>11.130578512396696</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
         <f>'Historical Data'!$U26</f>
-        <v>0.3165885714285715</v>
+        <v>0.31711878787878778</v>
       </c>
       <c r="C5">
         <f>'Historical Data'!$U27</f>
-        <v>2.0805194805194839E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1.8967493112947687E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6">
         <f>'Historical Data'!$V26</f>
-        <v>0.41529809523809524</v>
+        <v>0.41469272727272727</v>
       </c>
       <c r="C6">
         <f>'Historical Data'!$V27</f>
-        <v>3.3972294372294379E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3.3226446280991695E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <f>'Historical Data'!$W26</f>
-        <v>94.228571428571442</v>
+        <v>92.818181818181827</v>
       </c>
       <c r="C7">
         <f>'Historical Data'!$W27</f>
-        <v>58.067532467532466</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>59.920661157024789</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8">
         <f>'Historical Data'!$X26</f>
-        <v>7.663492063492062</v>
+        <v>7.7131313131313117</v>
       </c>
       <c r="C8">
         <f>'Historical Data'!$X27</f>
-        <v>5.3454545454545466</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>4.9553719008264467</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9">
         <f>'Historical Data'!$Y26</f>
-        <v>4.3037047619047613</v>
+        <v>4.2237151515151519</v>
       </c>
       <c r="C9">
         <f>'Historical Data'!$Y27</f>
-        <v>-8.6045021645021633E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-7.2483746556473813E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
         <f>'Historical Data'!$Z26</f>
-        <v>1.2834761904761904</v>
+        <v>1.2728787878787879</v>
       </c>
       <c r="C10">
         <f>'Historical Data'!$Z27</f>
-        <v>-1.4143722943722932E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-1.1739944903581261E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11">
         <f>'Historical Data'!$AA26</f>
-        <v>2.7619619047619035</v>
+        <v>2.7432848484848491</v>
       </c>
       <c r="C11">
         <f>'Historical Data'!$AA27</f>
-        <v>9.4032900432900468E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8.5868870523415963E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <f>'Historical Data'!$AB26</f>
-        <v>18.377777777777769</v>
+        <v>20.131313131313135</v>
       </c>
       <c r="C12">
         <f>'Historical Data'!$AB27</f>
-        <v>6.7887445887445885</v>
+        <v>6.3763085399449029</v>
       </c>
     </row>
   </sheetData>

--- a/included/leaguehistory.xlsx
+++ b/included/leaguehistory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aflyn\repos\Baseball\FantasySgpSystem\included\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C6EC73-EF51-4371-A353-82E32C902D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A723A8-34D1-4AF8-888E-3C3069356DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4695" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CDE96B8F-12BE-474E-931C-48604B977C2E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CDE96B8F-12BE-474E-931C-48604B977C2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -513,9 +513,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -527,6 +524,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3147,8 +3147,8 @@
         <v>92.818181818181827</v>
       </c>
       <c r="X26" s="7">
-        <f>(12*SLOPE(X4:X13,$P$4:$P$13)+INTERCEPT(X4:X13,$P$4:$P$13))/9</f>
-        <v>7.7131313131313117</v>
+        <f>(12*SLOPE(X4:X13,$P$4:$P$13)+INTERCEPT(X4:X13,$P$4:$P$13))/8</f>
+        <v>8.6772727272727259</v>
       </c>
       <c r="Y26" s="7">
         <f>(12*SLOPE(Y4:Y13,$P$4:$P$13)+INTERCEPT(Y4:Y13,$P$4:$P$13))</f>
@@ -3163,8 +3163,8 @@
         <v>2.7432848484848491</v>
       </c>
       <c r="AB26" s="7">
-        <f>(12*SLOPE(AB4:AB13,$P$4:$P$13)+INTERCEPT(AB4:AB13,$P$4:$P$13))/3</f>
-        <v>20.131313131313135</v>
+        <f>(12*SLOPE(AB4:AB13,$P$4:$P$13)+INTERCEPT(AB4:AB13,$P$4:$P$13))/4</f>
+        <v>15.098484848484851</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4965,22 +4965,22 @@
       <c r="A51">
         <v>2024</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24" t="s">
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="I51" s="24"/>
-      <c r="J51" s="24"/>
-      <c r="K51" s="24"/>
-      <c r="L51" s="24"/>
-      <c r="M51" s="24"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
     </row>
     <row r="52" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="20" t="s">
@@ -6008,496 +6008,496 @@
       <c r="M80" s="29"/>
     </row>
     <row r="81" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="25" t="s">
+      <c r="B81" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C81" s="25" t="s">
+      <c r="C81" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D81" s="25" t="s">
+      <c r="D81" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="E81" s="25" t="s">
+      <c r="E81" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F81" s="25" t="s">
+      <c r="F81" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="25" t="s">
+      <c r="G81" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="25" t="s">
+      <c r="H81" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="I81" s="25" t="s">
+      <c r="I81" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J81" s="25" t="s">
+      <c r="J81" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="K81" s="25" t="s">
+      <c r="K81" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L81" s="25" t="s">
+      <c r="L81" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="M81" s="25" t="s">
+      <c r="M81" s="24" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="26">
+      <c r="B82" s="25">
         <v>1010</v>
       </c>
-      <c r="C82" s="26">
+      <c r="C82" s="25">
         <v>290</v>
       </c>
-      <c r="D82" s="26">
+      <c r="D82" s="25">
         <v>1004</v>
       </c>
-      <c r="E82" s="26">
+      <c r="E82" s="25">
         <v>217</v>
       </c>
-      <c r="F82" s="26">
+      <c r="F82" s="25">
         <v>0.31259999999999999</v>
       </c>
-      <c r="G82" s="26">
+      <c r="G82" s="25">
         <v>0.432</v>
       </c>
-      <c r="H82" s="26">
+      <c r="H82" s="25">
         <v>1627</v>
       </c>
-      <c r="I82" s="26">
+      <c r="I82" s="25">
         <v>105</v>
       </c>
-      <c r="J82" s="26">
+      <c r="J82" s="25">
         <v>3.7679999999999998</v>
       </c>
-      <c r="K82" s="26">
+      <c r="K82" s="25">
         <v>1.222</v>
       </c>
-      <c r="L82" s="26">
+      <c r="L82" s="25">
         <v>2.8439999999999999</v>
       </c>
-      <c r="M82" s="26">
+      <c r="M82" s="25">
         <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="26">
+      <c r="B83" s="25">
         <v>1045</v>
       </c>
-      <c r="C83" s="26">
+      <c r="C83" s="25">
         <v>264</v>
       </c>
-      <c r="D83" s="26">
+      <c r="D83" s="25">
         <v>949</v>
       </c>
-      <c r="E83" s="26">
+      <c r="E83" s="25">
         <v>181</v>
       </c>
-      <c r="F83" s="26">
+      <c r="F83" s="25">
         <v>0.33779999999999999</v>
       </c>
-      <c r="G83" s="26">
+      <c r="G83" s="25">
         <v>0.4325</v>
       </c>
-      <c r="H83" s="26">
+      <c r="H83" s="25">
         <v>1534</v>
       </c>
-      <c r="I83" s="26">
+      <c r="I83" s="25">
         <v>98</v>
       </c>
-      <c r="J83" s="26">
+      <c r="J83" s="25">
         <v>3.7229999999999999</v>
       </c>
-      <c r="K83" s="26">
+      <c r="K83" s="25">
         <v>1.177</v>
       </c>
-      <c r="L83" s="26">
+      <c r="L83" s="25">
         <v>3.306</v>
       </c>
-      <c r="M83" s="26">
+      <c r="M83" s="25">
         <v>114</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="26">
+      <c r="B84" s="25">
         <v>961</v>
       </c>
-      <c r="C84" s="26">
+      <c r="C84" s="25">
         <v>261</v>
       </c>
-      <c r="D84" s="26">
+      <c r="D84" s="25">
         <v>908</v>
       </c>
-      <c r="E84" s="26">
+      <c r="E84" s="25">
         <v>225</v>
       </c>
-      <c r="F84" s="26">
+      <c r="F84" s="25">
         <v>0.32529999999999998</v>
       </c>
-      <c r="G84" s="26">
+      <c r="G84" s="25">
         <v>0.42009999999999997</v>
       </c>
-      <c r="H84" s="26">
+      <c r="H84" s="25">
         <v>1424</v>
       </c>
-      <c r="I84" s="26">
+      <c r="I84" s="25">
         <v>97</v>
       </c>
-      <c r="J84" s="26">
+      <c r="J84" s="25">
         <v>4.141</v>
       </c>
-      <c r="K84" s="26">
+      <c r="K84" s="25">
         <v>1.2450000000000001</v>
       </c>
-      <c r="L84" s="26">
+      <c r="L84" s="25">
         <v>3.1429999999999998</v>
       </c>
-      <c r="M84" s="26">
+      <c r="M84" s="25">
         <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="26">
+      <c r="B85" s="25">
         <v>1024</v>
       </c>
-      <c r="C85" s="26">
+      <c r="C85" s="25">
         <v>294</v>
       </c>
-      <c r="D85" s="26">
+      <c r="D85" s="25">
         <v>979</v>
       </c>
-      <c r="E85" s="26">
+      <c r="E85" s="25">
         <v>157</v>
       </c>
-      <c r="F85" s="26">
+      <c r="F85" s="25">
         <v>0.34239999999999998</v>
       </c>
-      <c r="G85" s="26">
+      <c r="G85" s="25">
         <v>0.44500000000000001</v>
       </c>
-      <c r="H85" s="26">
+      <c r="H85" s="25">
         <v>1717</v>
       </c>
-      <c r="I85" s="26">
+      <c r="I85" s="25">
         <v>111</v>
       </c>
-      <c r="J85" s="26">
+      <c r="J85" s="25">
         <v>3.7349999999999999</v>
       </c>
-      <c r="K85" s="26">
+      <c r="K85" s="25">
         <v>1.2190000000000001</v>
       </c>
-      <c r="L85" s="26">
+      <c r="L85" s="25">
         <v>2.7559999999999998</v>
       </c>
-      <c r="M85" s="26">
+      <c r="M85" s="25">
         <v>121</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="26">
+      <c r="B86" s="25">
         <v>1049</v>
       </c>
-      <c r="C86" s="26">
+      <c r="C86" s="25">
         <v>279</v>
       </c>
-      <c r="D86" s="26">
+      <c r="D86" s="25">
         <v>982</v>
       </c>
-      <c r="E86" s="26">
+      <c r="E86" s="25">
         <v>167</v>
       </c>
-      <c r="F86" s="26">
+      <c r="F86" s="25">
         <v>0.32379999999999998</v>
       </c>
-      <c r="G86" s="26">
+      <c r="G86" s="25">
         <v>0.42559999999999998</v>
       </c>
-      <c r="H86" s="26">
+      <c r="H86" s="25">
         <v>1453</v>
       </c>
-      <c r="I86" s="26">
+      <c r="I86" s="25">
         <v>92</v>
       </c>
-      <c r="J86" s="26">
+      <c r="J86" s="25">
         <v>3.6480000000000001</v>
       </c>
-      <c r="K86" s="26">
+      <c r="K86" s="25">
         <v>1.2050000000000001</v>
       </c>
-      <c r="L86" s="26">
+      <c r="L86" s="25">
         <v>2.996</v>
       </c>
-      <c r="M86" s="26">
+      <c r="M86" s="25">
         <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="27">
+      <c r="B87" s="26">
         <v>1031</v>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="26">
         <v>336</v>
       </c>
-      <c r="D87" s="27">
+      <c r="D87" s="26">
         <v>1077</v>
       </c>
-      <c r="E87" s="27">
+      <c r="E87" s="26">
         <v>68</v>
       </c>
-      <c r="F87" s="27">
+      <c r="F87" s="26">
         <v>0.32269999999999999</v>
       </c>
-      <c r="G87" s="27">
+      <c r="G87" s="26">
         <v>0.44169999999999998</v>
       </c>
-      <c r="H87" s="27">
+      <c r="H87" s="26">
         <v>1679</v>
       </c>
-      <c r="I87" s="27">
+      <c r="I87" s="26">
         <v>106</v>
       </c>
-      <c r="J87" s="27">
+      <c r="J87" s="26">
         <v>3.73</v>
       </c>
-      <c r="K87" s="27">
+      <c r="K87" s="26">
         <v>1.2050000000000001</v>
       </c>
-      <c r="L87" s="27">
+      <c r="L87" s="26">
         <v>3.476</v>
       </c>
-      <c r="M87" s="27">
+      <c r="M87" s="26">
         <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="26">
+      <c r="B88" s="25">
         <v>1008</v>
       </c>
-      <c r="C88" s="26">
+      <c r="C88" s="25">
         <v>290</v>
       </c>
-      <c r="D88" s="26">
+      <c r="D88" s="25">
         <v>944</v>
       </c>
-      <c r="E88" s="26">
+      <c r="E88" s="25">
         <v>121</v>
       </c>
-      <c r="F88" s="26">
+      <c r="F88" s="25">
         <v>0.3266</v>
       </c>
-      <c r="G88" s="26">
+      <c r="G88" s="25">
         <v>0.44090000000000001</v>
       </c>
-      <c r="H88" s="26">
+      <c r="H88" s="25">
         <v>1504</v>
       </c>
-      <c r="I88" s="26">
+      <c r="I88" s="25">
         <v>94</v>
       </c>
-      <c r="J88" s="26">
+      <c r="J88" s="25">
         <v>4.266</v>
       </c>
-      <c r="K88" s="26">
+      <c r="K88" s="25">
         <v>1.2589999999999999</v>
       </c>
-      <c r="L88" s="26">
+      <c r="L88" s="25">
         <v>2.972</v>
       </c>
-      <c r="M88" s="26">
+      <c r="M88" s="25">
         <v>108</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="26">
+      <c r="B89" s="25">
         <v>917</v>
       </c>
-      <c r="C89" s="26">
+      <c r="C89" s="25">
         <v>263</v>
       </c>
-      <c r="D89" s="26">
+      <c r="D89" s="25">
         <v>899</v>
       </c>
-      <c r="E89" s="26">
+      <c r="E89" s="25">
         <v>143</v>
       </c>
-      <c r="F89" s="26">
+      <c r="F89" s="25">
         <v>0.32050000000000001</v>
       </c>
-      <c r="G89" s="26">
+      <c r="G89" s="25">
         <v>0.43090000000000001</v>
       </c>
-      <c r="H89" s="26">
+      <c r="H89" s="25">
         <v>1171</v>
       </c>
-      <c r="I89" s="26">
+      <c r="I89" s="25">
         <v>80</v>
       </c>
-      <c r="J89" s="26">
+      <c r="J89" s="25">
         <v>3.867</v>
       </c>
-      <c r="K89" s="26">
+      <c r="K89" s="25">
         <v>1.2130000000000001</v>
       </c>
-      <c r="L89" s="26">
+      <c r="L89" s="25">
         <v>3.165</v>
       </c>
-      <c r="M89" s="26">
+      <c r="M89" s="25">
         <v>124</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="26">
+      <c r="B90" s="25">
         <v>1016</v>
       </c>
-      <c r="C90" s="26">
+      <c r="C90" s="25">
         <v>329</v>
       </c>
-      <c r="D90" s="26">
+      <c r="D90" s="25">
         <v>1029</v>
       </c>
-      <c r="E90" s="26">
+      <c r="E90" s="25">
         <v>193</v>
       </c>
-      <c r="F90" s="26">
+      <c r="F90" s="25">
         <v>0.33189999999999997</v>
       </c>
-      <c r="G90" s="26">
+      <c r="G90" s="25">
         <v>0.46010000000000001</v>
       </c>
-      <c r="H90" s="26">
+      <c r="H90" s="25">
         <v>1148</v>
       </c>
-      <c r="I90" s="26">
+      <c r="I90" s="25">
         <v>63</v>
       </c>
-      <c r="J90" s="26">
+      <c r="J90" s="25">
         <v>3.7029999999999998</v>
       </c>
-      <c r="K90" s="26">
+      <c r="K90" s="25">
         <v>1.228</v>
       </c>
-      <c r="L90" s="26">
+      <c r="L90" s="25">
         <v>3.1030000000000002</v>
       </c>
-      <c r="M90" s="26">
+      <c r="M90" s="25">
         <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="26">
+      <c r="B91" s="25">
         <v>931</v>
       </c>
-      <c r="C91" s="26">
+      <c r="C91" s="25">
         <v>257</v>
       </c>
-      <c r="D91" s="26">
+      <c r="D91" s="25">
         <v>856</v>
       </c>
-      <c r="E91" s="26">
+      <c r="E91" s="25">
         <v>190</v>
       </c>
-      <c r="F91" s="26">
+      <c r="F91" s="25">
         <v>0.32279999999999998</v>
       </c>
-      <c r="G91" s="26">
+      <c r="G91" s="25">
         <v>0.41070000000000001</v>
       </c>
-      <c r="H91" s="26">
+      <c r="H91" s="25">
         <v>1181</v>
       </c>
-      <c r="I91" s="26">
+      <c r="I91" s="25">
         <v>91</v>
       </c>
-      <c r="J91" s="26">
+      <c r="J91" s="25">
         <v>4.0979999999999999</v>
       </c>
-      <c r="K91" s="26">
+      <c r="K91" s="25">
         <v>1.24</v>
       </c>
-      <c r="L91" s="26">
+      <c r="L91" s="25">
         <v>2.601</v>
       </c>
-      <c r="M91" s="26">
+      <c r="M91" s="25">
         <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="26">
+      <c r="B92" s="25">
         <v>889</v>
       </c>
-      <c r="C92" s="26">
+      <c r="C92" s="25">
         <v>259</v>
       </c>
-      <c r="D92" s="26">
+      <c r="D92" s="25">
         <v>891</v>
       </c>
-      <c r="E92" s="26">
+      <c r="E92" s="25">
         <v>102</v>
       </c>
-      <c r="F92" s="26">
+      <c r="F92" s="25">
         <v>0.32729999999999998</v>
       </c>
-      <c r="G92" s="26">
+      <c r="G92" s="25">
         <v>0.43070000000000003</v>
       </c>
-      <c r="H92" s="26">
+      <c r="H92" s="25">
         <v>1595</v>
       </c>
-      <c r="I92" s="26">
+      <c r="I92" s="25">
         <v>120</v>
       </c>
-      <c r="J92" s="26">
+      <c r="J92" s="25">
         <v>3.3319999999999999</v>
       </c>
-      <c r="K92" s="26">
+      <c r="K92" s="25">
         <v>1.141</v>
       </c>
-      <c r="L92" s="26">
+      <c r="L92" s="25">
         <v>3.282</v>
       </c>
-      <c r="M92" s="26">
+      <c r="M92" s="25">
         <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B93" s="28">
+      <c r="B93" s="27">
         <v>852</v>
       </c>
-      <c r="C93" s="28">
+      <c r="C93" s="27">
         <v>188</v>
       </c>
-      <c r="D93" s="28">
+      <c r="D93" s="27">
         <v>776</v>
       </c>
-      <c r="E93" s="28">
+      <c r="E93" s="27">
         <v>161</v>
       </c>
-      <c r="F93" s="28">
+      <c r="F93" s="27">
         <v>0.32840000000000003</v>
       </c>
-      <c r="G93" s="28">
+      <c r="G93" s="27">
         <v>0.41249999999999998</v>
       </c>
-      <c r="H93" s="28">
+      <c r="H93" s="27">
         <v>963</v>
       </c>
-      <c r="I93" s="28">
+      <c r="I93" s="27">
         <v>43</v>
       </c>
-      <c r="J93" s="28">
+      <c r="J93" s="27">
         <v>3.7429999999999999</v>
       </c>
-      <c r="K93" s="28">
+      <c r="K93" s="27">
         <v>1.175</v>
       </c>
-      <c r="L93" s="28">
+      <c r="L93" s="27">
         <v>3.8210000000000002</v>
       </c>
-      <c r="M93" s="28">
+      <c r="M93" s="27">
         <v>124</v>
       </c>
     </row>
@@ -6505,40 +6505,40 @@
       <c r="A94">
         <v>2025</v>
       </c>
-      <c r="B94" s="25" t="s">
+      <c r="B94" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C94" s="25" t="s">
+      <c r="C94" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D94" s="25" t="s">
+      <c r="D94" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="25" t="s">
+      <c r="E94" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F94" s="25" t="s">
+      <c r="F94" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G94" s="25" t="s">
+      <c r="G94" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="H94" s="25" t="s">
+      <c r="H94" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="I94" s="25" t="s">
+      <c r="I94" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J94" s="25" t="s">
+      <c r="J94" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="K94" s="25" t="s">
+      <c r="K94" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L94" s="25" t="s">
+      <c r="L94" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="M94" s="25" t="s">
+      <c r="M94" s="24" t="s">
         <v>13</v>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="B8">
         <f>'Historical Data'!$X26</f>
-        <v>7.7131313131313117</v>
+        <v>8.6772727272727259</v>
       </c>
       <c r="C8">
         <f>'Historical Data'!$X27</f>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B12">
         <f>'Historical Data'!$AB26</f>
-        <v>20.131313131313135</v>
+        <v>15.098484848484851</v>
       </c>
       <c r="C12">
         <f>'Historical Data'!$AB27</f>
